--- a/Final_Evaluation_Report_Gemma (1).xlsx
+++ b/Final_Evaluation_Report_Gemma (1).xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\engma\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D38F7D83-BCD8-4644-894B-0E9F751E2ED7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4BADD738-E329-4F54-8C77-480BAAE6B1E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="262" uniqueCount="190">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="202" uniqueCount="142">
   <si>
     <t>Date</t>
   </si>
@@ -71,10 +71,10 @@
     <t>verdict</t>
   </si>
   <si>
-    <t>2026-01-26 06:26:32</t>
-  </si>
-  <si>
-    <t>&lt;CAN=DwnvXoVAbEEo+sMU3MUDSAwv_kPH3++80jumfWkDRev9nxQ@mail.gmail.com&gt;</t>
+    <t>2026-01-28 16:35:12</t>
+  </si>
+  <si>
+    <t>&lt;CAN=Dwnvo2gRhdtWu-K2q7tieZZc3ZkeBs20mLV6sR=Kr2RmEuw@mail.gmail.com&gt;</t>
   </si>
   <si>
     <t>xmio.511x@gmail.com</t>
@@ -84,7 +84,7 @@
   </si>
   <si>
     <t xml:space="preserve">*نفيد سعادتكم تعطل وحدات تكييف الاسبلت في الدور الثاني بمبنى مركز شرطة
-العريجاء، حيث تسبب العطل في  ارتفاع ملحوظ في درجات الحرارة داخل المكاتب
+العريجاء، حيث تسبب العطل في ارتفاع ملحوظ في درجات الحرارة داخل المكاتب
 الإدارية وأثر سلباً على سير العمل وبيئة الموظفين**.*
 *عليه، نأمل من سعادتكم التوجيه لمن يلزم بسرعة وقوف الفرق الفنية المختصة على
 الموقع، وإجراء الصيانة اللازمة وإصلاح العطل بصفة عاجلة لضمان استمرارية
@@ -95,38 +95,54 @@
 </t>
   </si>
   <si>
-    <t>**الموضوع:** رد على البلاغ حول تعطل وحدات التكييف في دور ثاني مركز شرطة العريجاء  
-السيد العقيد / محمد  
-مدير مركز شرطة العريجاء  
-تحية طيبة وبعد،
-نود أن نشكركم على تواصلكم السريع والتقرير المقدم حول تعطل وحدات التكييف من نوع الأسبلت في الدور الثاني بمبنى مركز الشرطة، والذي تسبب في ارتفاع درجات الحرارة داخل المكاتب الإدارية وأثر سلبًا على البيئة العملية.
-بناءً على ما ورد في البلاغ، فإننا نؤكد على وجوب معالجة هذا العطل فورًا، وفقًا للإجراءات المنصوص عليها في **الفقرة 65 من الشروط والمواصفات الفنية** المتعلقة بأعمال الصيانة الطارئة، وخاصة البند **7-3-ب**، والذي يُلزم المقاول بتوفير الفنيين فور تلقي البلاغ وإجراء الصيانة اللازمة.
-لذلك:
-1. تم التواصل فوريًا مع **شركة واحة صقر لعربيّة للتجارة والمقاولات**، وهي الشركة المنفذة لخدمات الصيانة والتشغيل بموجب **العقد الخاص بمركز شرطة العريجاء** تحت مشروع "صيانة وتشغيل المواقع الأمنية بمنطقة الرياض (المرحلة الثالثة)".
-2. تم توجيه الشركة بإرسال فريق فني مؤهل إلى الموقع فورًا لإجراء الفحص والصيانة الضرورية، وتحديد سبب العطل وتقديم تقرير فني مفصل حوله.
-3. في حال استدعى الأمر استخدام قطع غيار، ستتحمل الشركة المسؤولية الكاملة وفقًا للبنود التعاقدية، وفي حال تأخر التنفيذ، سيتم تطبيق الغرامات وفقًا للفقرة **3-1/1 و3-1/3**، والتي تتراوح بين 500 ريال يوميًا حسب مدة التأخير وعدم الالتزام بالجدولة الزمنية.
-4. سنقوم بمتابعة تنفيذ الإصلاح عن كثب، وسيتم إعلامكم فور انتهاء العمل وعودته إلى وضعه الطبيعي.
-نؤكد لكم أننا نعطي أولوية كاملة لمعالجة مثل هذه الحالات التي تؤثر على سير العمل وبيئة الموظفين، وسنحرص على تفعيل البنود القانونية والفنية المعتمدة في العقود لتوفير أفضل مستويات الخدمة.
+    <t>السيد / مدير شركة واحة صقر لعروبة للتجارة والمقاولات المنفذة للعقد:  
+"عملية صيانة ونظافة وتشغيل المواقع الأمنية التابعة للأمن العام بمنطقة الرياض (المرحلة الثالثة)"  
+السلام عليكم ورحمة الله وبركاته،،،  
+نُخطركم علمًا بوجود عطل طارئ في وحدات تكييف الأسبلت في الدور الثاني بمبنى مركز شرطة العريجاء، وقد تسبب ذلك في ارتفاع ملحوظ في درجات الحرارة داخل المكاتب الإدارية، مما أدى إلى تأثير سلبي واضح على بيئة العمل وسير العمليات الإدارية.  
+بناءً على ما ورد إلينا، فإننا نؤكد لكم أنه يجب عليكم إرسال فريق فني فوري إلى الموقع لتقييم العطل وإصلاحه بشكل عاجل، وعدم التأخّر في التعامل مع هذه المشكلة، لما لها من تأثير مباشر على أداء العمل وبيئة الموظفين.  
+ونلفت انتباهكم إلى وجوب الحرص على تنفيذ الأعمال بصدد الجدول الزمني المحدد، والتزام الشركة بكافة الشروط التعاقدية المتعلقة بتوفير الخدمة الفورية في حال حدوث أعطال طارئة.  
 وتقبلو تحياتي  
 مدير قسم الإشراف</t>
   </si>
   <si>
-    <t>السادة / شركة واحة صقر لعروبة للتجارة والمقاولات المنفذة للعقد: عملية صيانة ونظافة وتشغيل المواقع الأمنية التابعة للأمن العام بمنطقة الرياض (المرحلة الثالثة) السلام عليكم ورحمة الله وبركاته،،،  نُخطركم علمًا بوجود عطل طارئ في **وحدات تكييف الأسبلت في الدور الثاني بمبنى مركز شرطة العريجاء**، وقد تسبب ذلك في **ارتفاع ملحوظ في درجات الحرارة داخل المكاتب الإدارية**، مما أدى إلى **تأثير سلبي واضح على بيئة العمل وسير العمليات الإدارية**.  بناءً على ما ورد إلينا، فإننا **نؤكد لكم أنه يجب عليكم إرسال فريق فني فوري إلى الموقع لتقييم العطل وإصلاحه بشكل عاجل**، وعدم التأخر في التعامل مع هذه المشكلة، لما لها من تأثير مباشر على أداء العمل وبيئة الموظفين. نلفت انتباهكم إلى **الفقرة 3-1/1** من الشروط والمواصفات الفنية، والتي تنص على فرض **غرامة قدرها 500 ريال يوميًا** عن كل جهاز أو نظام يظل العطل فيه قائماً، خاصة إذا كان ذلك يؤثر على ظروف العمل المحيطية. كذلك، نذكركم بأنه في حال تم إبلاغكم عن العطل ولم تتدخلوا إلا بعد مضي **أكثر من 12 ساعة**، فإنه سيتم **فرض الغرامة كاملة دون خصم**، ولن يُنظر إلى أي ذريعة أو تبرير. نؤكد لكم أن أي تأخير أو إهمال في التعامل مع هذا العطل سيكون له آثار قانونية ومالية مباشرة على عقدكم، وسيتم اتخاذ الإجراءات المناسبة وفقًا للبنود التعاقدية. وتقبلوا تحياتي،، مدير قسم الإشراف</t>
-  </si>
-  <si>
-    <t xml:space="preserve">مسودة البوت تفتقر إلى صرامة الرد النموذجي. الرد النموذجي أكثر صرامة في تحديد المسؤوليات وتتضمن تهديدات أكثر بخصوص الغرامات. </t>
-  </si>
-  <si>
-    <t>مسودة البوت تحتوي على بعض الأخطاء اللغوية البسيطة، مثل استخدام كلمة "فوريًا" بدلاً من "فورًا" في بعض الأماكن. الرد النموذجي أكثر دقة في استخدام اللغة ويشمل بعض العبارات الرسمية التي تزيد من صرامة الرد.</t>
+    <t xml:space="preserve">السادة / شركة واحة صقر لعروبة للتجارة والمقاولات المنفذة للعقد: عملية
+صيانة ونظافة وتشغيل المواقع الأمنية التابعة للأمن العام بمنطقة الرياض
+(المرحلة الثالثة)
+السلام عليكم ورحمة الله وبركاته،،،
+نُخطركم علمًا بوجود عطل طارئ في وحدات تكييف الأسبلت في الدور الثاني
+بمبنى مركز شرطة العريجاء وقد تسبب ذلك في ارتفاع ملحوظ في درجات الحرارة
+داخل المكاتب الإدارية مما أدى إلى تأثير سلبي واضح على بيئة العمل وسير
+العمليات الإدارية.
+بناءً على ما ورد إلينا، فإننا نؤكد لكم أنه يجب عليكم إرسال فريق فني
+فوري إلى الموقع لتقييم العطل وإصلاحه بشكل عاجل، وعدم التأخر في التعامل
+مع هذه المشكلة، لما لها من تأثير مباشر على أداء العمل وبيئة الموظفين.
+نلفت انتباهكم إلى الفقرة 3-1/1 من الشروط والمواصفات الفنية، والتي تنص
+على فرض غرامة قدرها 500 ريال يوميًا عن كل جهاز أو نظام يظل العطل فيه
+قائماً، خاصة إذا كان ذلك يؤثر على ظروف العمل المحيطية.
+كذلك، نذكركم بأنه في حال تم إبلاغكم عن العطل ولم تتدخلوا إلا بعد مضي
+أكثر من 12 ساعة، فإنه سيتم فرض الغرامة كاملة دون خصم، ولن يُنظر إلى أي
+ذريعة أو تبرير.
+نؤكد لكم أن أي تأخير أو إهمال في التعامل مع هذا العطل سيكون له آثار
+قانونية ومالية مباشرة على عقدكم، وسيتم اتخاذ الإجراءات المناسبة وفقًا
+للبنود التعاقدية.
+وتقبلوا تحياتي،،
+مدير قسم الإشراف
+</t>
+  </si>
+  <si>
+    <t>تمت الإشارة إلى الفقرة 3-1/1 من الشروط والمواصفات الفنية في الرد النموذجي، والتي تنص على فرض غرامة عن التأخير في الإصلاح. كما تم إضافة نص حول فرض الغرامة كاملة في حال التأخير عن 12 ساعة.  لم يتم ذكر هذه التفاصيل في مسودة البوت.</t>
+  </si>
+  <si>
+    <t>لا توجد أخطاء لغوية بارزة في مسودة البوت.</t>
   </si>
   <si>
     <t>يحتاج تعديل</t>
   </si>
   <si>
-    <t>2026-01-26 06:28:42</t>
-  </si>
-  <si>
-    <t>&lt;CAN=DwntdtozC8BBGjK5ZATBHWr4vt=kZuS+t94Y-a35WuD1-7w@mail.gmail.com&gt;</t>
+    <t>2026-01-28 16:37:34</t>
+  </si>
+  <si>
+    <t>&lt;CAN=DwnuVGJkwE7iJ7nDbhtq=jOmPbVs=7zzeUqOCs5TRzno34w@mail.gmail.com&gt;</t>
   </si>
   <si>
     <t xml:space="preserve">نفيد سعادتكم بتعطل بعض وحدات الانارة في قاعة الاجتماعات بالمبنى طرفنا حيث
@@ -139,66 +155,57 @@
 </t>
   </si>
   <si>
-    <t>السيد / مدير الصيانة  
-شركة صقور العرب للمقاولات العامة  
-السلام عليكم ورحمة الله وبركاته  
-إشارة إلى بلاغ مقدم من مدير مركز شرطة الملز حول **تعطل بعض وحدات الإضاءة في قاعة الاجتماعات بالمبنى**، وهو ما يؤثر مباشرةً على سير العمليات الإدارية والاجتماعات اليومية التي تعقد في تلك القاعة، فقد تم توجيه إنذار رسمي إليكم بشأن هذا الشأن.
-بناءً على البنود التعاقدية وخاصة **الفقرة 65 من العقد** المتعلقة بمسؤوليات المقاول في **الصيانة الطارئة والعاجلة**، فإننا **نقترح بقوة** أن تقوموا فورًا بإرسال فريق فني مؤهل إلى الموقع لإجراء الصيانة الضرورية وإصلاح وحدات الإضاءة المعطّلة، وذلك ضمن **التوقيت المحدد (12 ساعة)** من تاريخ تسلم هذا البلاغ.
-كما نلفت انتباهكم إلى أن **التقصير في الوفاء بالتزامات العقد قد يؤدي إلى تطبيق الغرامات المالية بمعدل 500 ريال سعودي يوميًا**، وفقًا للبنود التعاقدية المتفق عليها.
-ونؤكد على ضرورة **إشعارنا بكافة الإجراءات المتخذة والتقارير الفنية** فور انتهاء الصيانة، بهدف متابعتها وتوثيقها.
+    <t>السادة / شركة صقور العرب للمقاولات العامة المنفذة للعقد: عملية صيانة ونظافة وتشغيل المواقع الأمنية التابعة للأمن العام بمنطقة الرياض (المرحلة الثانية)  
+السلام عليكم ورحمة الله وبركاته،،،  
+نُخطركم علمًا بوجود عطل طارئ في **بعض وحدات الإضاءة في قاعة الاجتماعات بمبنى مركز شرطة الملز**، وهو أمر مستجد رغم وجود بلاغ سابق تم رفعه حول ذات الموضوع، إلا أن الشركة لم تستجب له بشكل فعال، مما أدى إلى تفاقم الوضع وتأثيره السلبي على سير العمل الرسمي.  
+بناءً على ما ورد إلينا، فإننا **نؤكد لكم أنه يجب عليكم إرسال فريق فني فوري إلى الموقع لتقييم العطل وإصلاحه بشكل عاجل**، وعدم التسويف أو تقديم أي ذريعة تؤخر تنفيذ الخدمة، لما لذلك من تأثير مباشر على استخدام القاعة لاجتماعات هامة تتعلق بسير الأعمال الإدارية والأمنية.  
+نلفت انتباهكم إلى الفقرتين **(١٢-أ)** و**(٣٥-ب)** من العقد الموقع بين الطرفين، اللواتي تحددان التزام الشركة بتقديم خدمات الصيانة الطارئة في الوقت المناسب، وفي حال حدوث أي تأخير بدون مبرر مشروع، سيتم تطبيق الغرامات اليومية وفقًا للبنود النظامية، ولن يُنظر لأي اعتذار أو تبرير.  
+كما نُعيد التنويه بأن أي تقصير في الالتزام بالوقت أو الجودة قد يؤدي إلى **تطبيق آثار قانونية مباشرة**، بما فيها إنهاء العلاقة التعاقدية إذا دعت الحاجة.  
+**ننتظر تأكيدكم على توفر الفريق الفني في الموقع خلال ساعة واحدة من تاريخ استلام هذا الإشعار**، وإلا سنقوم بإتخاذ الإجراءات النظامية الفورية.  
 وتقبلو تحياتي  
 مدير قسم الإشراف</t>
   </si>
   <si>
-    <t>السادة / شركة صقور العرب للمقاولات العامة المنفذة للعقد: عملية صيانة ونظافة وتشغيل المواقع الأمنية التابعة للأمن العام بمنطقة الرياض (المرحلة الثانية) السلام عليكم ورحمة الله وبركاته،،، نُخطركم علمًا بوجود عطل طارئ في **بعض وحدات الإضاءة في قاعة الاجتماعات بمبنى مركز شرطة الملز**، وهو أمر يستدعي تدخلًا فوريًا، خاصة وأن تلك القاعة تستخدم بشكل يومي لإجراء الاجتماعات الهامة، ولا يمكن التسامح مع هذا التقصير الذي يؤثر سلبًا على سير العمل واستخدام المنشآت الأساسية. بناءً على ما ورد إلينا، فإننا **نؤكد لكم أنه يجب عليكم إرسال فريق فني فوري إلى الموقع لتقييم العطل وإصلاحه بشكل عاجل**، وعدم التأخير في التعامل مع هذه المشكلة، لما لها من تأثير مباشر على أداء العمل وفعالية التواصل التنظيمي. نلفت انتباهكم إلى **الفقرة 65 من اللائحة المتعلقة بالتشغيل والصيانة للأعمال الكهربائية**، والتي توجب على المقاول القيام باستبدال القطع أو الأجزاء أو الأجهزة التالفة أو المحترقة وتأمين ما يلزم من الوقود والزيوت والشحومات وخلافه، وفقًا للأصول الفنية المتبعة وتعليمات الشركات الصانعة. كذلك، نذكركم بأنه **مقتضب الفقرة (ب) ضمن نفس الفقرة 65**، أن على المقاول تنسيق سجلات إجراءات الصيانة على هيئة نظام للجداول البيانية الجدارية، والسماح بالتخطيط المستقبلي لتلبية الاحتياجات المهنية، وهو ما لم يتم الالتزام به أيضًا في هذا الملف. نحذركم بشدة من التكرار أو التباطؤ في المستقبل، إذ سيعرضكم ذلك إلى الغرامات المالية والتقارير الرسمية أمام الجهات المختصة**. وتقبلوا تحياتي،، مدير قسم الإشراف</t>
-  </si>
-  <si>
-    <t>مسودة البوت أقل صرامة في الطلب على الإصلاح الفوري. الرد النموذجي أكثر تحديدًا في تحديد المسؤوليات ويشير إلى التزامات محددة من العقد.</t>
-  </si>
-  <si>
-    <t>مسودة البوت تحتوي على بعض الأخطاء اللغوية البسيطة، مثل استخدام 'السلام عليكم ورحمة الله وبركاته' مرتين. الرد النموذجي أكثر دقة في استخدام اللغة ويبين بنية جمل أكثر قوة.</t>
-  </si>
-  <si>
-    <t>2026-01-26 06:31:13</t>
-  </si>
-  <si>
-    <t>&lt;CAN=Dwnv2DOABih+ucqu44JzpoxOSQfh8k8RuvjqM7P_0YAJ5aA@mail.gmail.com&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">نفيد سعادتكم بوجود تسريبات مياه في الدور الأرضي مما تسبب في توقف خدمة
-المياه بشكل جزئي كما يؤدي لهدر المياه .
-امل توجيه من ترونه حيال اصلاح اعمال السباكة عاجلا .
-شاكرين ومقدرين لكم تعاونكم الدائم.
-*مدير مركز شرطة* الملز
-*عقيد / محمد*
-</t>
-  </si>
-  <si>
-    <t>السيد / مدير شركة صقور العرب للمقاولات العامة  
-المنفذة للعقد: عملية صيانة ونظافة وتشغيل المواقع الأمنية التابعة للأمن العام بمنطقة الرياض (المرحلة الثانية)
-السلام عليكم ورحمة الله وبركاته،،،  
-نُخطركم علمًا بوجود **تسريبات مياه في الدور الأرضي بمبنى مركز شرطة الملز**، وقد أدت هذه التسريبات إلى **توقف جزئي لخدمة المياه**، بالإضافة إلى **هدر كبير في المياه**، مما يعكس تقصيرًا في أداء الخدمات التعاقدية المتفق عليها.
-بناءً على ما ورد إلينا، فإننا **نؤكد لكم بأنه يجب عليكم إرسال فريق فني فوري إلى الموقع لتقييم العطل وإصلاحه بشكل عاجل**، وعدم التأخير في التعامل مع هذه المشكلة، لما لها من تأثير مباشر على سير العمليات الإدارية والخدمات الأساسية.
-نلفت انتباهكم إلى **الفقرة 65 – 1/7 من اللائحة الخاصة بالصيانة الكهربائية والميكانيكية**، والتي تنص على ضرورة **معالجة حالات التسرب فورًا**، وضرورة **إبلاغ الجهات المعنية فور ظهور أي تسرب أو انسداد** بهدف اتخاذ الإجراءات الفورية.
-كذلك، نشير إلى أن **التقاعس في التنفيذ أو التأخير في إنجاز الصيانة يعتبر مخالفًا لبنود العقد**، وبالتالي سيتم **تطبيق الغرامات المالية بموجب البندين 65 و3-1/1 من العقد**، وذلك بمعدل **500 ريال سعودي يوميًا** في حالة التأخير دون مسوّغ مشروع.
-رجاءً تفضلوا بالإبلاغ عن اسم الفريق الفني الذي سيقوم بالزيارة، وعن توقيت الوصول المتوقع، وتفاصيل الإصلاح المقترحة.
-وتقبلو تحياتي  
-مدير قسم الإشراف</t>
-  </si>
-  <si>
-    <t>السادة شركة صقور العرب للمقاولات العامة** السلام عليكم ورحمة الله وبركاته: بناءً على البلاغ الوارد من مركز شرطة الملز، فإن هناك تسريبات مياه في الدور الأرضي أدت إلى توقف جزئي لخدمة المياه وهدر في كميات كبيرة من المياه. ونظرًا لخطورة هذا العطل وتأثيره السلبي على الخدمات الأساسية، **نشدد على ضرورة توجيه فريق فني فوري إلى الموقع لفحص وتحديد مواقع التسريب وإجراء الصيانة والإصلاح العاجل دون أي تأخير**، طبقًا للفقرة 65 أ-10 من الشروط التعاقدية المتعلقة بأعمال الفواصل والعزل لتسرب المياه، والتي تنص على معالجة التسريبات فور ظهورها. كما نحذر من أن أي تأخير في تنفيذ الإصلاح سيعرض الشركة إلى تطبيق الغرامات وفق الأنظمة الناظمة للعقود. وتقبلوا تحياتي،  مدير قسم الإشراف</t>
-  </si>
-  <si>
-    <t>الرد النموذجي أكثر دقة في تحديد الإجراءات المطلوبة، ويشدد على ضرورة الفحص وتحديد مواقع التسريب.  يُفضل استخدام لغة أكثر رسمية في الرد النموذجي.</t>
-  </si>
-  <si>
-    <t>مسودة البوت تحتوي على بعض الأخطاء اللغوية البسيطة، مثل استخدام علامات الترقيم بشكل غير صحيح. الرد النموذجي أكثر دقة في استخدام اللغة العربية الفصحى.</t>
-  </si>
-  <si>
-    <t>2026-01-26 06:33:38</t>
-  </si>
-  <si>
-    <t>&lt;CAN=DwnvaC6LNNT8LtpJ_kbxvxueHYaKTDF4DW1tG56BSwVo=Lw@mail.gmail.com&gt;</t>
+    <t xml:space="preserve">السادة / شركة صقور العرب للمقاولات العامة المنفذة للعقد: عملية صيانة
+ونظافة وتشغيل المواقع الأمنية التابعة للأمن العام بمنطقة الرياض
+(المرحلة الثانية)
+السلام عليكم ورحمة الله وبركاته،،،
+نُخطركم علمًا بوجود عطل طارئ في **بعض وحدات الإضاءة في قاعة الاجتماعات
+بمبنى مركز شرطة الملز**، وهو أمر مستجد رغم وجود بلاغ سابق تم رفعه حول
+ذات الموضوع، إلا أن الشركة لم تستجب له بشكل فعال، مما أدى إلى تفاقم
+الوضع وتأثيره السلبي على سير العمل الرسمي.
+بناءً على ما ورد إلينا، فإننا **نؤكد لكم أنه يجب عليكم إرسال فريق فني
+فوري إلى الموقع لتقييم العطل وإصلاحه بشكل عاجل**، وعدم التسويف أو
+تقديم أي ذريعة تؤخر تنفيذ الخدمة، لما لذلك من تأثير مباشر على استخدام
+القاعة لاجتماعات هامة تتعلق بسير الأعمال الإدارية والأمنية.
+نلفت انتباهكم إلى الفقرتين **(١٢-أ)** و**(٣٥-ب)** من العقد الموقع بين
+الطرفين، اللواتي تحددان التزام الشركة بتقديم خدمات الصيانة الطارئة في
+الوقت المناسب، وفي حال حدوث أي تأخير بدون مبرر مشروع، سيتم تطبيق
+الغرامات اليومية وفقًا للبنود النظامية، ولن يُنظر لأي اعتذار أو تبرير.
+كما نُعيد التنويه بأن أي تقصير في الالتزام بالوقت أو الجودة قد يؤدي
+إلى **تطبيق آثار قانونية مباشرة**، بما فيها إنهاء العلاقة التعاقدية
+إذا دعت الحاجة.
+**ننتظر تأكيدكم على توفر الفريق الفني في الموقع خلال ساعة واحدة من
+تاريخ استلام هذا الإشعار**، وإلا سنقوم بإتخاذ الإجراءات النظامية
+الفورية.
+وتقبلو تحياتي
+مدير قسم الإشراف
+</t>
+  </si>
+  <si>
+    <t>لا توجد فروقات في الإجراء</t>
+  </si>
+  <si>
+    <t xml:space="preserve">هناك بعض الفروقات الطفيفة في التنسيق، مثل إزالة بعض الفواصل الزائدة. </t>
+  </si>
+  <si>
+    <t>ناجح</t>
+  </si>
+  <si>
+    <t>2026-01-28 16:42:35</t>
+  </si>
+  <si>
+    <t>&lt;CAN=DwnsSLfRW+1KghTW5y4YjzgndTaubQsZhV+6EYwrvrFz_mQ@mail.gmail.com&gt;</t>
   </si>
   <si>
     <t xml:space="preserve">*نفيد سعادتكم، بتعطل مضخة الحريق* *في المستودع رقم (3)، حيث لوحظ انخفاض حاد
@@ -212,33 +219,50 @@
 </t>
   </si>
   <si>
-    <t>السيد / مدير شركة واحة صقر لعرابة للتجارة والمقاولات المنفذة للعقد:  
-عملية صيانة وتشغيل المواقع الأمنية التابعة للأمن العام بمنطقة الرياض (المرحلة الثالثة)
-السلام عليكم ورحمة الله وبركاته:
-نُخطركم علمًا بوجود **عطل طارئ في مضخة الحريق في المستودع رقم (3)**، حيث لوحظ **انخفاض حاد في ضغط شبكة المياه المخصصة لمكافحة الحريق**، مما أدى إلى **توقف نظام الإطفاء التلقائي عن العمل بالشكل المطلوب**، ويشكل هذا العطل تهديداً حقيقياً لسلامة التجهيزات والبنية التحتية للمستودع.
-بناءً على ما ورد إلينا، فإننا **نؤكد لكم بأنه يجب عليكم إرسال فريق فني فوري إلى الموقع لتقييم العطل وإصلاحه بشكل عاجل**، وعدم التأخير في التعامل مع هذه المشكلة، لما لها من تأثير مباشر على سلامة العمليات اللوجستية والاحتياجات الأمنية.
-نلفت انتباهكم إلى **الفقرة 3-1/1 من الشروط التعاقدية**، والتي تنص على فرض غرامة قدرها **500 ريال يومياً** عن كل جهاز أو نظام يظل العطل قائماً فيه، وخاصة فيما يتعلق بالأعطال التي تؤثر على خدمات أساسية مثل أنظمة مكافحة الحريق.
-**إن أي تأخير في التنفيذ سيعرض الشركة إلى تطبيق الغرامات وفق الأحكام القانونية والتعاقدية المعمول بها**.
+    <t>السيد / شركة صقور العرب للمقاولات العامة  
+السلام عليكم ورحمة الله وبركاته:  
+بناءً على البلاغ الوارد من مدير مستودعات الأمن الدبلوماسي، فقد تم تأكيد وجود عطل طارئ في مضخة الحريق في المستودع رقم (3)، والذي أدى إلى انخفاض حاد في ضغط شبكة المياه المخصصة لمكافحة الحريق، وبالتالي توقف نظام الإطفاء التلقائي عن العمل بالشكل المطلوب، وهو ما يمثل تهديدًا مباشرًا لسلامة التجهيزات والمنشآت.  
+وبحسب الفقرة 65 أ-10 من الشروط التعاقدية، والتزامًا بما ورد في الفقرة 65 7-3-ب حول الصيانة الطارئة، فإنه **يجب** على الشركة توجيه فريق فني فوري إلى الموقع لفحص مضخة الحريق وإجراء الصيانة والإصلاح العاجل دون أي تأخير، وتحقيق استعادة النظام إلى حالته التشغيلية الكاملة.  
+كما نؤكد أنه **لا يُنظر لأي ذريعة** فيما يتعلق بتكرار مثل هذه الحالات، وأن أي تأخر في التنفيذ سيُعتبر مخالفًا لبنود العقد، وسيترتب عليه **تطبيق الغرامات وفق البندين 3-1/1 و3-1/2 من الفقرة 65**، اللذين يربطان بين التزام المقاول بالوقت والخدمة الفورية، ويمنحان حق فرض غرامات يومية مباشرة في حال التأخر.  
+وعلينا تحذير الشركة بأنه في حال تكرار مثل هذه الأعطال أو التأخير في الإصلاح، ستتخذ الإجراءات القانونية المناسبة، بما في ذلك **فرض الغرامات اليومية بمعدل 500 ريال يوميًا**، وقد تصل إلى إنهاء العقد في حال تكرار المخالفات.  
+ونحن إذ نوجهكم إلى تنفيذ الأوامر السابقة فورًا، فإننا ننتظر تقريرًا فنيًا مفصلاً عن سبب العطل والإجراءات المتخذة لإزالته، مع توثيق القطع المعيبة إن وُجدت.  
 وتقبلو تحياتي  
 مدير قسم الإشراف</t>
   </si>
   <si>
-    <t>السادة شركة صقر العروبة للمقاولات العامة المنفذة للعقد: عملية صيانة وتشغيل المواقع الأمنية التابعة للأمن العام بمنطقة الرياض (المرحلة الثالثة) السلام عليكم ورحمة الله وبركاته: نُخطركم علمًا بوجود عطل طارئ في مضخة الحريق في المستودع رقم (3)**، حيث لوحظ **انخفاض حاد في ضغط شبكة المياه المخصصة لمكافحة الحريق**، مما أدى إلى **توقف نظام الإطفاء التلقائي عن العمل بالشكل المطلوب**، ويشكل هذا العطل تهديداً حقيقياً لسلامة التجهيزات والبنية التحتية للمستودع. بناءً على ما ورد إلينا، فإننا **نؤكد لكم بأنه يجب عليكم إرسال فريق فني فوري إلى الموقع لتقييم العطل وإصلاحه بشكل عاجل**، وعدم التأخير في التعامل مع هذه المشكلة، لما لها من تأثير مباشر على سلامة العمليات اللوجستية والاحتياجات الأمنية. نلفت انتباهكم إلى **الفقرة 3-1/1 من الشروط التعاقدية**، والتي تنص على فرض غرامة قدرها 500 ريال يومياً** عن كل جهاز أو نظام يظل العطل قائماً فيه، وخاصة فيما يتعلق بالأعطال التي تؤثر على خدمات أساسية مثل أنظمة مكافحة الحريق. إن أي تأخير في التنفيذ سيعرض الشركة إلى تطبيق الغرامات وفق الأحكام القانونية والتعاقدية المعمول بها. وتقبلوا تحياتي  مدير قسم الإشراف</t>
-  </si>
-  <si>
-    <t>لا توجد فروقات في الإجراء</t>
-  </si>
-  <si>
-    <t>لا توجد أخطاء لغوية</t>
-  </si>
-  <si>
-    <t>ناجح</t>
-  </si>
-  <si>
-    <t>2026-01-26 06:35:44</t>
-  </si>
-  <si>
-    <t>&lt;CAN=Dwnsh_0v0VwYRhdD3Srjuwga_Tc_hM5ioCEfCzPjuzERfZw@mail.gmail.com&gt;</t>
+    <t xml:space="preserve">السادة شركة صقر العروبة للمقاولات العامة المنفذة للعقد: عملية صيانة
+وتشغيل المواقع الأمنية التابعة للأمن العام بمنطقة الرياض (المرحلة
+الثالثة)
+السلام عليكم ورحمة الله وبركاته:
+نُخطركم علمًا بوجود عطل طارئ في مضخة الحريق في المستودع رقم (3)، حيث
+لوحظ انخفاض حاد في ضغط شبكة المياه المخصصة لمكافحة الحريق، مما أدى إلى
+توقف نظام الإطفاء التلقائي عن العمل بالشكل المطلوب، ويشكل هذا العطل
+تهديداً حقيقياً لسلامة التجهيزات والبنية التحتية للمستودع.
+بناءً على ما ورد إلينا، فإننا نؤكد لكم بأنه يجب عليكم إرسال فريق فني
+فوري إلى الموقع لتقييم العطل وإصلاحه بشكل عاجل، وعدم التأخير في
+التعامل مع هذه المشكلة، لما لها من تأثير مباشر على سلامة العمليات
+اللوجستية والاحتياجات الأمنية.
+نلفت انتباهكم إلى الفقرة 3-1/1 من الشروط التعاقدية، والتي تنص على فرض
+غرامة قدرها 500 ريال يومياً عن كل جهاز أو نظام يظل العطل قائماً فيه،
+وخاصة فيما يتعلق بالأعطال التي تؤثر على خدمات أساسية مثل أنظمة مكافحة
+الحريق.
+إن أي تأخير في التنفيذ سيعرض الشركة إلى تطبيق الغرامات وفق الأحكام
+القانونية والتعاقدية المعمول بها.
+وتقبلوا تحياتي
+مدير قسم الإشراف
+</t>
+  </si>
+  <si>
+    <t>الرد النموذجي أكثر دقة في تحديد المهام المطلوبة من الشركة، ويوضح بشكل أفضل العواقب القانونية والتعاقدية في حال التأخير. مسودة البوت تستخدم لغة أكثر صرامة وتهديدًا.</t>
+  </si>
+  <si>
+    <t>مسودة البوت تحتوي على بعض الأخطاء اللغوية البسيطة، مثل استخدام 'يجب' بشكل مفرط. الرد النموذجي أكثر دقة في استخدام اللغة ويسير بشكل أكثر احترافية.</t>
+  </si>
+  <si>
+    <t>2026-01-28 16:45:45</t>
+  </si>
+  <si>
+    <t>&lt;CAN=DwntyD9JS9-vtkzw_cdrcgTHKPHeH-hRzp4EZD1NuGLt_4g@mail.gmail.com&gt;</t>
   </si>
   <si>
     <t xml:space="preserve">*سعادة مدير إدارة المشاريع - سلمه الله* *نفيد سعادتكم،* بحدوث خلل فني في
@@ -252,23 +276,52 @@
 </t>
   </si>
   <si>
-    <t>السيد / مدير شركة واحة صقر لعروبة للتجارة والمقاولات المنفذة للعقد:  
-"عملية صيانة ونظافة وتشغيل المواقع الأمنية التابعة للأمن العام بمنطقة الرياض (المرحلة الثالثة)"  
-السلام عليكم ورحمة الله وبركاته:  
-بناءً على البلاغ الوارد من **مدير مركز انطلاق دوريات أمن طرق الساند**، فإن هناك **خللاً فنياً في المصدات الأمنية عند المدخل الرئيسي للمركز**، حيث تم لحظ **تهريب في زيت الهيدروليك من البساتم وعدم استجابة المصدة لأوامر الرفع**، مما تسبب في **إعاقة حركة دخول وخروج دوريات أمن الطرق**، ويُعتبر هذا العطل **ثغرة أمنية مباشرة** تستدعي التدخل العاجل.  
-ونظرًا لخطورة هذا العطل وتأثيره السلبي على سلامة العمليات الأمنية والحركة المرورية، **نشدد على ضرورة إرسال فريق فني فوري إلى الموقع لفحص وتحديد مصدر التهريب وإصلاح المصدات الأمنية بشكل عاجل**، طبقًا للفقرة **65 – 7-1** من الشروط التعاقدية الخاصة بإدارة الصيانة الوقائية والفنية للمصدات الأمنية الهيدروليكية، والتي تنص على وجوب التفاعل السريع مع أي عطل يهدد الأداء أو السلامة.  
-كما **نحذر من أن أي تأخير في التنفيذ سي تعرض الشركة إلى غرامات تقدر بـ 500 ريال سعودي يومياً**، وفق الأنظمة الناظمة للعقود.  
+    <t>السيد/ مدير إدارة المشاريع - سلمه الله  
+السلام عليكم ورحمة الله وبركاته،
+بناءً على البلاغ الوارد من مركز انطلاق دوريات أمن طرق الساند، فقد تم الإبلاغ عن وجود خلل فني في المصدات الأمنية عند المدخل الرئيسي، حيث لوحظ تهريب في زيت الهيدروليك من البساتم وعدم استجابة المصدة لأوامر الرفع، مما أدى إلى إعاقة حركة دخول وخروج دوريات أمن الطرق، وبالتالي تشكل ثغرة أمنية خطيرة.
+ونظرًا لخطورة هذا العطل وتأثيره المباشر على سلامة الموقع وأمن العمليات اللوجستية، فإننا نوجهكم فورًا بتوجيه فريق فني مختص من شركة "واحة صقر لعروبة للتجارة والمقاولات" إلى الموقع لإجراء الصيانة الطارئة اللازمة، وفقًا للفقرة 65/7-3-أ من الشروط التعاقدية الخاصة بالصيانة الشهرية والطارئة، والتي تنص على وجوب التحرك الفوري في حالة حدوث أعطال طارئة.
+كما نلفت انتباهكم إلى الفقرة 65/7-3-ب من نفس الشروط، والتي توضح أنه في حالة حدوث عطل طارئ، يجب على المقاول إرسال الفنيين فورًا بعد الإبلاغ، وإعداد تقرير فني مفصل حول العطل، مع تحديد ما إذا كانت هناك حاجة إلى قطع غيار أو خدمات خاصة.
+نؤكد لكم أن أي تأخير في التنفيذ سيُعتبر مخالفة واضحة لبنود العقد، وسيتم تطبيق الغرامات وفقًا للبندين التاليين:
+- **البند 10/3**: المسؤوليات التعاقدية للشركة المنفذة، والذي يشمل التزامها بالإصلاح الفوري دون تأخير.
+- **البند 10/9**: الغرامات المالية في حالة التقصير في الالتزامات التعاقدية، والتي سيتم تطبيقها يوميًا حتى يتم حل المشكلة.
+نؤكد مرة أخرى أن هذا العطل يُعد طارئًا ويحتاج إلى تدخل فوري، ولا يُنظر لأي ذريعة تتعلق بطبيعة العطل أو مدى تعقيده، إذ أن السلامة والأمن أولوية قصوى، ولن يُسمح بأي تأخير قد يؤدي إلى تفاقم الوضع أو تعرض الموقع لخطر محتمل.
+ننتظر تأكيد توجيه فريق الصيانة إلى الموقع فورًا، وفي حال تأخر الشركة المنفذة عن الوفاء بهذا الالتزام، سيتم اتخاذ الإجراءات النظامية المناسبة، بما فيها تطبيق الغرامات ورفع الموضوع أمام الجهات المختصة.
 وتقبلو تحياتي  
 مدير قسم الإشراف</t>
   </si>
   <si>
-    <t>السادة شركة صقر العروبة للمقاولات العامة المنفذة للعقد:  "عملية صيانة ونظافة وتشغيل المواقع الأمنية التابعة للأمن العام بمنطقة الرياض (المرحلة الثالثة)"  السلام عليكم ورحمة الله وبركاته:  بناءً على البلاغ الوارد من **مدير مركز انطلاق دوريات أمن طرق الساند**، فإن هناك **خللاً فنياً في المصدات الأمنية عند المدخل الرئيسي للمركز**، حيث تم لحظ **تهريب في زيت الهيدروليك من البساتم وعدم استجابة المصدة لأوامر الرفع**، مما تسبب في **إعاقة حركة دخول وخروج دوريات أمن الطرق**، ويُعتبر هذا العطل **ثغرة أمنية مباشرة** تستدعي التدخل العاجل.  ونظرًا لخطورة هذا العطل وتأثيره السلبي على سلامة العمليات الأمنية والحركة المرورية، **نشدد على ضرورة إرسال فريق فني فوري إلى الموقع لفحص وتحديد مصدر التهريب وإصلاح المصدات الأمنية بشكل عاجل**، طبقًا للفقرة **65 – 7-1** من الشروط التعاقدية الخاصة بإدارة الصيانة الوقائية والفنية للمصدات الأمنية الهيدروليكية، والتي تنص على وجوب التفاعل السريع مع أي عطل يهدد الأداء أو السلامة.  كما نحذر من أن أي تأخير في التنفيذ سي تعرض الشركة إلى غرامات تقدر بـ 500 ريال سعودي يومياً**، وفق الأنظمة الناظمة للعقود.  وتقبلوا تحياتي  مدير قسم الإشراف</t>
-  </si>
-  <si>
-    <t>2026-01-26 06:38:11</t>
-  </si>
-  <si>
-    <t>&lt;CAN=DwntxeUxL0T2egLEMOhbVdSkAL9UrqLq_4pNKw5SaR9JvYQ@mail.gmail.com&gt;</t>
+    <t xml:space="preserve">السادة شركة صقر العروبة للمقاولات العامة المنفذة للعقد:
+"عملية صيانة ونظافة وتشغيل المواقع الأمنية التابعة للأمن العام بمنطقة
+الرياض (المرحلة الثالثة)"
+السلام عليكم ورحمة الله وبركاته:
+بناءً على البلاغ الوارد من مدير مركز انطلاق دوريات أمن طرق الساند، فإن
+هناك خللاً فنياً في المصدات الأمنية عند المدخل الرئيسي للمركز، حيث تم
+لوحظ تهريب في زيت الهيدروليك من البساتم وعدم استجابة المصدة لأوامر
+الرفع، مما تسبب في إعاقة حركة دخول وخروج دوريات أمن الطرق، ويُعتبر هذا
+العطل ثغرة أمنية مباشرة تستدعي التدخل العاجل.
+ونظرًا لخطورة هذا العطل وتأثيره السلبي على سلامة العمليات الأمنية
+والحركة المرورية، نشدد على ضرورة إرسال فريق فني فوري إلى الموقع لفحص
+وتحديد مصدر التهريب وإصلاح المصدات الأمنية بشكل عاجل، طبقًا للفقرة 65
+– 7-1 من الشروط التعاقدية الخاصة بإدارة الصيانة الوقائية والفنية
+للمصدات الأمنية الهيدروليكية، والتي تنص على وجوب التفاعل السريع مع أي
+عطل يهدد الأداء أو السلامة.
+كما نحذر من أن أي تأخير في التنفيذ سيتعرض الشركة إلى غرامات تقدر بـ
+500 ريال سعودي يومياً، وفق الأنظمة الناظمة للعقود.
+وتقبلوا تحياتي
+مدير قسم الإشراف
+</t>
+  </si>
+  <si>
+    <t>الرد النموذجي أكثر تركيزًا على الخطورة الفورية للعطل ويشدد على ضرورة التدخل العاجل.  يحدد أيضًا الغرامات المحددة في العقد. مسودة البوت أكثر طولًا وتتضمن تفاصيل إضافية غير ضرورية.</t>
+  </si>
+  <si>
+    <t>مسودة البوت تحتوي على بعض الأخطاء اللغوية البسيطة، مثل استخدام 'بناءً على البلاغ الوارد' بدلاً من 'بناءً على البلاغ الوارد من'. الرد النموذجي أكثر دقة في استخدام اللغة.</t>
+  </si>
+  <si>
+    <t>2026-01-28 16:47:52</t>
+  </si>
+  <si>
+    <t>&lt;CAN=DwnuVbDmcOrQeUeKOg+5yHtJ5HgzFw4V4Nh2gDuHvnAr+qQ@mail.gmail.com&gt;</t>
   </si>
   <si>
     <t xml:space="preserve">السلام عليكم ورحمة الله وبركاته :
@@ -281,62 +334,35 @@
 </t>
   </si>
   <si>
-    <t>السيد / مدير شركة واحة صقر لعرابة للتجارة والمقاولات المنفذة للعقد:  
-"عملية صيانة ونظافة وتشغيل المواقع الأمنية التابعة للأمن العام بمنطقة الرياض (المرحلة الثالثة)"  
-السلام عليكم ورحمة الله وبركاته:  
-بناءً على البلاغ الوارد من **مدير مركز شرطة البطحاء**، فإنه تم **استحداث عددٍ من المكاتب الجديدة ضمن نطاق الإدارة**، وبالتالي **توجد حاجة ملحة لتأمين الأثاث والمكاتب اللازمة لمواكبة متطلبات العمل**.  
-ونحن إذ نحيطكم علمًا بهذا الوضع، فإننا **نطالب بتوفير الأثاث اللازم بما يتوافق مع مواصفات البنية التحتية للموقع**، وذلك خلال فترة زمنية لا تتعدى الأيام الثلاثة القادمة، وبحسب الأولوية المطلوبة لضمان استمرارية العمليات الإدارية.  
-ونلفت النظر إلى أهمية الالتزام بالجدولة الزمنية المطلوبة، والتواصل المباشر مع إدارة المركز لتحديد أماكن التركيب وتفاصيل الأثاث المطلوب.  
+    <t>السيد / عقيد محمد – مدير مركز شرطة البطحاء  
+السلام عليكم ورحمة الله وبركاته:
+نحيطكم علمًا بأنه لا يمكن تزويدكم بالأثاث أو المكاتب الجديدة ضمن نطاق العقود الحالية الخاصة بصيانة ونظافة وتشغيل المواقع الأمنية، إذ إن هذه العقود لا تتضمن خدمات تركيب أو توريد الأثاث أو المعدات الإدارية.
+وعليه، يرجى التنسيق مع إدارة الإمدادات والتوريدات في الأمن العام لتلبية الحاجة المطلوبة وفق الإجراءات النظامية والموارد المالية المخصصة لهذه الغاية.
 وتقبلو تحياتي  
 مدير قسم الإشراف</t>
   </si>
   <si>
-    <t>سعادة مدير مركز شرطة البطحاء السلام عليكم ورحمة الله وبركاته : إشارة الى ايميلكم الوارد والمتضمن استحداث مكاتب في الإدارة طرفكم وطلب تأمين اثاث ومكاتب . عليه نفيد سعادتكم ان ذلك لا يقع ضمن نطاق اعمالنا .لذا امل من سعادتكم مخاطبة جهة الاختصاص في ذلك .وتقبلوا تحياتي،  مدير قسم الإشراف</t>
-  </si>
-  <si>
-    <t>مسودة البوت تتضمن طلبًا غير مناسب، بينما الرد النموذجي يرفض الطلب بشكل صحيح ويوجه إلى جهة مختصة.</t>
-  </si>
-  <si>
-    <t>بعض الجمل في مسودة البوت طويله بعض الشيء ويمكن تحسينها من حيث البساطة.</t>
-  </si>
-  <si>
-    <t>2026-01-26 06:40:42</t>
-  </si>
-  <si>
-    <t>&lt;CAN=Dwns7i1YT+xB9=NwX+dv760k8ScV_UUiFtF_2TW9H22L43Q@mail.gmail.com&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">السلام عليكم ورحمة الله وبركاته :
-نظرا لاستحداث مكاتب جديدة لدينا في الإدارة، آمل من سعادتكم تأمين أثاث
-ومكاتب نظرا لحاجة العمل
-وتقبلو تحياتي
-*مدير مركز شرطة البطحاء *
-*عقيد / *
-*محمد*
-</t>
-  </si>
-  <si>
-    <t>السيد / مدير مركز شرطة البطحاء  
-السلام عليكم ورحمة الله وبركاته:
-إشارة إلى إيميلكم الكريم الوارد، والمتضمن طلب تأمين أثاث ومكاتب جديدة في الإدارة، نحيط سعادتكم بأنه لا يقع موضوع الطلب ضمن نطاق اختصاص قسم الإشراف، إذ إنه يرتبط بتوفير الأثاث والمعدات الداخلية، وهي مهام تخضع لإدارة أخرى مختصة بذلك.
-لذلك، نرجو من سعادتكم مخاطبة الجهة المختصة المسؤولة عن توفير الأثاث والمعدات الإدارية، وذلك لمعالجة الطلب بما يتوافق مع الإجراءات والصلاحيات المقررة.
-وتقبلو تحياتي  
-مدير قسم الإشراف</t>
-  </si>
-  <si>
-    <t>سعادة مدير مركز شرطة البطحاء السلام عليكم ورحمة الله وبركاته : إشارة الى ايميلكم الوارد والمتضمن استحداث مكاتب في الإدارة طرفكم وطلب تأمين اثاث ومكاتب . عليه نفيد سعادتكم ان ذلك لايقع ضمن نطاق اعمالنا . لذا امل من سعادتكم مخاطبة جهة الاختصاص في ذلك . وتقبلوا تحياتي،  مدير قسم الإشراف</t>
-  </si>
-  <si>
-    <t>الرد النموذجي أكثر اختصارًا ووضوحًا في بيان سبب رفض الطلب.  يُفضل استخدام لغة أكثر رسمية في الرد.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">الرد النموذجي يحتوي على بعض الأخطاء اللغوية البسيطة، مثل عدم استخدام الفواصل بشكل صحيح وبعض الأخطاء في النحو.  </t>
-  </si>
-  <si>
-    <t>2026-01-26 06:42:51</t>
-  </si>
-  <si>
-    <t>&lt;CAN=DwnsAp67zyVqmFxczcoLE8yLGhkmpvHvJoAUi2ExVW+g2xg@mail.gmail.com&gt;</t>
+    <t xml:space="preserve">سعادة مدير مركز شرطة البطحاء
+السلام عليكم ورحمة الله وبركاته :
+إشارة الى ايميلكم الوارد والمتضمن استحداث مكاتب في الإدارة طرفكم وطلب
+تأمين اثاث ومكاتب .
+عليه نفيد سعادتكم أن ذلك لا يقع ضمن نطاق أعمالنا .
+لذا آمل من سعادتكم مخاطبة جهة الاختصاص في ذلك .
+وتقبلوا تحياتي،
+مدير قسم الإشراف
+</t>
+  </si>
+  <si>
+    <t>الرد النموذجي أكثر دقة في تحديد المطلوب من البوت، حيث يحدد بوضوح أن الطلب يتعلق بـ 'استحداث مكاتب' و 'تأمين اثاث ومكاتب'.  يُفضل أن يذكر البوت في مسودته  'استحداث مكاتب' بدلاً من 'الأثاث أو المكاتب الجديدة' لوضوح أكبر.</t>
+  </si>
+  <si>
+    <t>الرد النموذجي أكثر دقة لغوياً، ويفضل استخدام 'إشارة الى' بدلاً من 'نحيطكم علمًا'.</t>
+  </si>
+  <si>
+    <t>2026-01-28 16:50:58</t>
+  </si>
+  <si>
+    <t>&lt;CAN=DwnubTxQoi_QHWqUmCbWkWQtjXmQQWBQsUqLnYhovk2WayQ@mail.gmail.com&gt;</t>
   </si>
   <si>
     <t xml:space="preserve">السلام عليكم ورحمة الله وبركاته:
@@ -349,27 +375,37 @@
 </t>
   </si>
   <si>
-    <t>سعادة مدير مركز شرطة الخليج  
-السلام عليكم ورحمة الله وبركاته:
-إشارة إلى إيميلكم الوارد والمتضمن طلب استحداث مكاتب جديدة في الإدارة وتأمين الأثاث والمكاتب، نفيد سعادتكم بأنه **لا يقع هذا الطلب ضمن نطاق الأعمال الموكولة إلى قسم الإشراف**.
-لذلك، نأمل من سعادتكم مخاطبة الجهة المختصة بهذا النوع من الطلبات، وذلك لضمان إنهائه وفق الإجراءات النظامية.
-وتقبلو تحياتي  
+    <t>سعادة مدير مركز شرطة الخليج
+السلام عليكم ورحمة الله وبركاته:
+إشارة إلى إيميلكم الكريم المؤرخ في تاريخ 28/1/1447هـ، والذي يتضمَّن طلب تأمين أثاث ومكاتب جديدة نتيجة استحداث مكاتب في الإدارة.
+نحيط سعادتكم بأنه لا يُمكن التعامل مع هذا النوع من الطلبات ضمن نطاق مسؤوليات قسم الإشراف، إذ إن موضوع تأمين الأثاث والمكاتب يُعد من اختصاص الجهة المختصة بالإدارة المالية أو الإنشاءات أو الإمدادات، حسب نوعية الحاجة وطبيعة الاستحداث.
+لذلك، نرجو من سعادتكم التواصل المباشر مع الجهة المختصة لدراسة الطلب والتوجيه به وفق الإجراءات النظامية.
+وتقبلوا فائق التقدير والتحية،  
 مدير قسم الإشراف</t>
   </si>
   <si>
-    <t>سعادة مدير مركز شرطة الخليج السلام عليكم ورحمة الله وبركاته : إشارة الى ايميلكم الوارد والمتضمن استحداث مكاتب في الإدارة طرفكم وطلب تأمين اثاث ومكاتب . عليه نفيد سعادتكم ان ذلك لايقع ضمن نطاق اعمالنا. لذا امل من سعادتكم مخاطبة جهة الاختصاص في ذلك .وتقبلوا تحياتي،  مدير قسم الإشراف</t>
-  </si>
-  <si>
-    <t>الرد النموذجي أكثر بساطة ووضوحاً في صياغة الطلب.  يُفضل استخدام عبارات أكثر مباشرةً مثل "إشارة إلى إيميلكم" بدلاً من "إشارة إلى إيميلكم الوارد".</t>
-  </si>
-  <si>
-    <t>الرد النموذجي يحتوي على بعض الأخطاء اللغوية البسيطة، مثل عدم استخدام الفاصلة بعد "السلام عليكم ورحمة الله وبركاته" و "إلى" بدلاً من "إلى".</t>
-  </si>
-  <si>
-    <t>2026-01-26 06:44:53</t>
-  </si>
-  <si>
-    <t>&lt;CAN=DwnuC2RgHjEpoj5rJmmE2nWvk=pmgih5MFGaP9KonVzEzJw@mail.gmail.com&gt;</t>
+    <t xml:space="preserve">سعادة مدير مركز شرطة الخليج
+السلام عليكم ورحمة الله وبركاته:
+إشارة إلى إيميلكم الكريم المؤرخ في تاريخ 28/1/1447هـ، والذي يتضمَّن
+طلب تأمين أثاث ومكاتب جديدة نتيجة استحداث مكاتب في الإدارة.
+نحيط سعادتكم بأنه لا يُمكن التعامل مع هذا النوع من الطلبات ضمن نطاق
+مسؤوليات قسم الإشراف، إذ إن موضوع تأمين الأثاث والمكاتب يُعد من اختصاص
+الجهة المختصة بالإدارة المالية أو الإنشاءات أو الإمدادات، حسب نوعية
+الحاجة وطبيعة الاستحداث.
+لذلك، نرجو من سعادتكم التواصل المباشر مع الجهة المختصة لدراسة الطلب
+والتوجيه به وفق الإجراءات النظامية.
+وتقبلوا فائق التقدير والتحية،
+مدير قسم الإشراف
+</t>
+  </si>
+  <si>
+    <t>لا توجد أخطاء لغوية</t>
+  </si>
+  <si>
+    <t>2026-01-28 16:53:35</t>
+  </si>
+  <si>
+    <t>&lt;CAN=DwntaqW9xa=82d80OgNrSuK48MyF-=tqkfcSQBqooBpR_Kw@mail.gmail.com&gt;</t>
   </si>
   <si>
     <t>INQUIRY</t>
@@ -384,78 +420,45 @@
 </t>
   </si>
   <si>
-    <t>سعادة مدير الإدارة العامة  
+    <t>سعادة مدير الإدارة العامة،  
 السلام عليكم ورحمة الله وبركاته:  
-إشارة إلى إيميلكم الكريم المؤرخ 2026/01/26 والمتضمن طلب معرفة ملخص البلاغات الخاصة بصيانة مركز شرطة الملز خلال اليومين الماضيين، نرفق لكم في المرفقات تقريراً مفصلاً يشمل قائمة البلاغات المسجلة، والتصرفات المتخذة بشأن كل منها، بالإضافة إلى حالة التنفيذ لكل بلاغ.  
-ونرجو أن يكون التقرير مرضياً ويحقق غرضكم الكريم.  
+إشارة إلى طلبكم الكريم حول معرفة بلاغات الصيانة التي حصلت في مركز شرطة الملز خلال اليومين الماضيين، نرفق لكم ملخصاً بذلك على النحو التالي:
+1. **بلاغ تسريبات مياه في الدور الأرضي**:  
+   - تمت متابعته فور تبلغه، وقد وجهت رسالة رسمية إلى شركة صقور العرب للمقاولات العامة بتاريخ 28/1/1447هـ، لإيفاد فريق فني فوري لفحص وعلاج التسريبات طبقاً للفقرة 65 أ-10 من الشروط التعاقدية، وذلك بسبب خطورة العطل وهدر المياه والتوقف الجزئي لخدمة المياه.
+2. **بلاغ خلل في المصدات الأمنية عند المدخل الرئيسي**:  
+   - تمت متابعته أيضاً فور تبلغه، ووجهت رسالة رسمية إلى نفس الشركة بتاريخ 28/1/1447هـ، لإيفاد فريق فني فوري لفحص وصيانة المصدات الأمنية الهيدروليكية، وفق الفقرة 65 – 7-1 من الشروط التعاقدية، نظراً لتأثيره السلبي على الحركة الأمنية والمرورية.
+3. **بلاغ تعطل مضخة الحريق في المستودع رقم (3)**:  
+   - تمت متابعته فور تبلغه، ووجهت رسالة رسمية إلى شركة صقور العرب للمقاولات العامة بتاريخ 28/1/1447هـ، لإيفاد فريق فني فوري لفحص وصيانة مضخة الحريق، وفق الفقرة 65 من الشروط التعاقدية، نظراً لخطورتها على سلامة البنية التحتية.
+وقد تم اتخاذ الإجراءات النظامية عبر التنسيق مع الشركات المختصة، مع ملاحظة عدم وجود أي تجاوب أولي حتى اللحظة، وهو ما يستدعي مزيداً من المتابعة المشددة.
 وتقبلوا تحياتي،  
 مدير قسم الإشراف</t>
   </si>
   <si>
-    <t>سعادة مدير الإدارة العامة، السلام عليكم ورحمة الله وبركاته، الإشارة إلى طلب سعادتكم بخصوص بلاغات الصيانة في مركز شرطة الملز خلال اليومين الماضيين، فإليك ملخص البلاغات والإجراءات المتخذة: بلاغ تعطل وحدات الإنارة في قاعة الاجتماعات: تم إرسال إشعار فوري إلى شركة صقور العرب للمقاولات العامة، وتم التأكيد على وجوب توجيه فريق فني لإصلاح المشكلة طبقًا للفقرة 65 من الشروط التعاقدية.  بلاغ تسريبات مياه في الدور الأرضي**: تم أيضًا إخطار نفس الشركة بإلحاح إصلاح التسريبات، وذلك وفق الفقرة 65 أ-10 من الشروط التعاقدية، مع تحذير من تطبيق الغرامات في حال التأخير. وتقبلوا تحياتي، مدير قسم الإشراف.</t>
-  </si>
-  <si>
-    <t>مسودة البوت لا تقدم ملخصاً للبلاغات والإجراءات المتخذة كما هو مطلوب في الرد النموذجي.  تحتوي فقط على إشارة إلى وجود تقرير مرفق.</t>
-  </si>
-  <si>
-    <t>لا توجد أخطاء لغوية بارزة.</t>
-  </si>
-  <si>
-    <t>2026-01-26 06:46:42</t>
-  </si>
-  <si>
-    <t>&lt;CAN=DwnsHBEa1oUKJ_-69czw_cUPCOmAuYQ2PhHdzU6eMQknz2Q@mail.gmail.com&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">*مدير قسم الاشراف*
-أتمنى أن تكون بخير. أكتب إليك اليوم بشأن مشكلة معقدة تتعلق بمشروعنا الحالي
-في بناء الهيكل المتعدد الطبقات، حيث يبدو أن هناك تداخلاً غامضاً بين العناصر
-الهيكلية والالتزامات التعاقدية. تخيل لو أننا نواجه تأخيراً غير متوقع في
-تفعيل المرحلة الأولى من التنفيذ، حيث يعتمد الاستقرار الهيكلي على توافر
-الموقع بالكامل، لكن هناك عوائق غير مرئية تحول دون ذلك، مثل اختلالات في
-الجدول الزمني الناتجة عن عوامل خارجية غير محددة بوضوح، مما يؤدي إلى إمكانية
-انهيار التوازن الإنشائي إذا لم يتم التعامل معها بطريقة استراتيجية.
-في هذا السياق، افترض أن الجهة المسؤولة قد تجاوزت الحدود الزمنية المعيارية
-لتسليم العناصر الأساسية، مما يثير تساؤلات حول الإجراءات التصحيحية الممكنة،
-خاصة إذا كان هذا التأخير يتجاوز الفترات المقبولة هندسياً، مثل تلك التي قد
-تؤدي إلى مخاطر في السلامة أو الكفاءة. هل هناك آلية غامضة للانسحاب أو إعادة
-تقييم الالتزامات دون فقدان الاستقرار الكلي للمشروع؟ هذا السيناريو يذكرني
-بمعادلات التوازن في الهندسة الإنشائية حيث يجب أن تكون القوى المتضادة
-متوازنة، لكن هنا، المتغيرات النظامية تبدو مشفرة وغير مباشرة.
-أرجو منك التفكير في هذا الأمر بعمق، ربما من خلال مراجعة الوثائق الرسمية
-المتعلقة بالالتزامات الهندسية والتعاقدية، وإخباري بأي رؤى قد تساعد في فك
-شيفرة هذه المشكلة المبهمة. هل يمكن أن يكون الحل مخفياً في فقرة معينة تتعلق
-بإدارة التأخيرات في عقود الإنشاءات؟
-مع خالص التحية، مهندس فيصل
-</t>
-  </si>
-  <si>
-    <t>سعادة المهندس فيصل المحترم،
-تحية طيبة وبعد،
-نود أن نوضح لك أنه في إطار ما ورد في رسالتك حول مشروع بناء الهيكل المتعدد الطبقات وما يرتبط به من تداخلات بين العناصر الهيكلية والالتزامات التعاقدية، فإننا نشير إلى أن النظام واضح في تحديد الإجراءات القانونية والإدارية المتعلقة بتلك الحالات.
-بناءً على ما ورد في **اللائحة المادة 133** من نظام المنافسات والمشتريات الحكومية، فإن للجهة الحكومية الحق في إنهاء العقد بالاتفاق مع المتعاقد في حال تأخرت الجهة الحكومية في تسليم موقع العمل للمقاول لمدة تزيد على المدة المحددة في الفقرة (2) من المادة (التاسعة والخمسين)، وبعد إبلاغ المتعاقد بذلك، ومضت ثلاثون يوماً دون قيام الجهة الحكومية بتسليم الموقع أو اتخاذ إجراءات مقبولة في سبيل ذلك.
-كذلك، وفي حال استمرت الجهة الحكومية في إيقاف كامل الأعمال لأسباب لا علاقة للمتعاقد بها مدة تتجاوز (180) يوماً من تاريخ خطاب الإيقاف، وبعد إبلاغ المتعاقد للجهة الحكومية لتمكينه من استئناف الأعمال، ومضت ثلاثون يوماً دون اتخاذ إجراءات مقبولة، فإن للجهة الحكومية حق إنهاء العقد بالاتفاق.
-بالإضافة إلى ذلك، نلفت النظر إلى أن **اللائحة المادة 127** تتيح تشكيل لجنة فنية لمعاينة الأعمال وإعداد محضر بالاشتراك مع المتعاقد لحصر الأعمال المنجزة ونسبة الإنجاز وتحديد أسباب ومعوقات التأخير في التنفيذ، وذلك في حال انتهت مدة العقد ولم يسلم المتعاقد الأعمال.
-أما بالنسبة لما ورد في رسالتك حول "آلية غامضة" للانسحاب أو إعادة تقييم الالتزامات دون فقدان الاستقرار الكلي للمشروع، فإننا نؤكد أن النظام لا يترك المجال للتفسير الغامض، وإنما يوفر أدوات واضحة للتعامل مع التأخيرات والتوقفات، سواء كانت بسبب الجهة الحكومية أو المقاول.
-ننوه أيضاً إلى أن **اللائحة المادة 96** تلزم الجهة الحكومية بتسليم موقع الأعمال في عقود الإنشاءات العامة خلال المدة المحددة، وإذا تأخرت، جاز للمتعاقد أن يطلب إنهاء العقد وفقاً لأحكام المادة (133).
-نأمل أن تجد في هذه المعلومات الإطار الواضح الذي يمكنك الاعتماد عليه في التعامل مع القضية، ونؤكد أن أي تأخير أو إيقاف للأعمال يستدعي إبلاغ الجهات المختصة بشكل رسمي وفوراً، مع توثيق الأسباب والإجراءات المتخذة.
-وتقبلو تحياتي  
-مدير قسم الإشراف</t>
-  </si>
-  <si>
-    <t>تحية طيبة وبعد، نحيطكم علمًا بأن التأخير في تسليم الموقع أو في إنجاز الأعمال من قبل الجهة الحكومية يُعد من الحالات التي تُنظَّم في نظام المنافسات والمشتريات الحكومية، ومن أبرز المواد المعنية: المادة 133 من اللائحة التنفيذية لنظام المنافسات والمشتريات الحكومية  تتيح للجهة الحكومية إنهاء العقد بالاتفاق مع المقاول إذا تأخرت الجهة في تسليم الموقع لمدة تزيد على المدة المحددة في الفقرة (2) من المادة (التاسعة والخمسين) من النظام، وبعد إبلاغ المقاول بذلك، ومضى (30) يومًا دون قيام الجهة بتسليم الموقع أو اتخاذ إجراءات مقبولة. كما يُمكن أيضًا إنهاء العقد إذا استمرت الجهة الحكومية في إيقاف كامل الأعمال لأسباب لا علاقة للمقاول بها مدة تتجاوز (180) يومًا. المادة 96 من اللائحة التنفيذية لنظام المنافسات والمشتريات الحكومية  تُحدد مدة تسليم الموقع من قبل الجهة الحكومية، وفي حال التأخير يُمكن للمقاول طلب إنهاء العقد وفق المادة (133) المشار إليها.الفقرة 63 من كراسة الشروط الخاصة   تجبر المقاول على الالتزام بالجدول الزمني المحدد ما لم تكن هناك أسباب خارجة عن إرادته ومقابلة بموافقة الجهة الحكومية.بناءً على ما سبق، يُمكن اتباع الآتي:  إبلاغ الجهة المسؤولة خطياً** بالتأخير المُسجَّل، وتحديد الأثر الهندسي الناتج عن هذا التأخير.طلب التفاوض على تعديل الجدول الزمني أو تعويض المقاول** وفقاً للمادة 113 من اللائحة، إذا تأثرت التكاليف أو تم تعطيل إتمام العقد.في حالة استمرار التأخير وتأثيره على السلامة أو الاستقرار الإنشائي، يُمكن **طلب إنهاء العقد بالاتفاق** وفق المادة 133 المشار إليها، مع توثيق جميع الملاحظات والمستندات الداعمة.نوصي بمراجعة وثائق العقد وكراسة الشروط الخاصة لتحديد البنود المتعلقة بإدارة التأخيرات وتحديد ما إذا كانت هناك آليات متفق عليها مسبقًا. وتقبلوا تحياتي إدارة المشاريع</t>
-  </si>
-  <si>
-    <t>الرد النموذجي أكثر تركيزًا على الخطوات العملية التي يجب اتخاذها عند التأخير، بينما مسودة البوت أكثر تركيزًا على شرح القوانين واللوائح. الرد النموذجي يقدم حلولًا أكثر ملموسة.</t>
-  </si>
-  <si>
-    <t>مسودة البوت تحتوي على بعض الجمل الطويلة والمُعقدة، مما قد يصعب قراءتها. الرد النموذجي أكثر بساطة ووضوحًا.</t>
-  </si>
-  <si>
-    <t>2026-01-26 06:48:44</t>
-  </si>
-  <si>
-    <t>&lt;CAN=Dwnsj7_OA8ykQ8uKCp0+F2+G2V7qoTXo_-DXJPpV_GYMuuA@mail.gmail.com&gt;</t>
+    <t xml:space="preserve">سعادة مدير الإدارة العامة،
+السلام عليكم ورحمة الله وبركاته،
+إشارة إلى طلب سعادتكم بخصوص بلاغات الصيانة في مركز شرطة الملز خلال
+اليومين الماضيين، فإليك ملخص البلاغات والإجراءات المتخذة:
+بلاغ تعطل وحدات الإنارة في قاعة الاجتماعات: تم إرسال مخاطبة شركة صقور
+العرب للمقاولات العامة، وتم التأكيد على وجوب توجيه فريق فني لإصلاح
+المشكلة طبقًا للفقرة 65 من الشروط التعاقدية.
+بلاغ تسريبات مياه في الدور الأرضي: تم مخاطبة الشركة بالحاجة لإصلاح
+التسريبات، وذلك وفق الفقرة 65 أ-10 من الشروط التعاقدية، مع تحذير من
+تطبيق الغرامات في حال التأخير.
+وتقبلوا تحياتي،
+مدير قسم الإشراف.
+</t>
+  </si>
+  <si>
+    <t>تحتوي مسودة البوت على معلومات إضافية غير ضرورية مثل تفاصيل تاريخ البلاغ وعدد المرة التي تم فيها مخاطبة الشركة. الرد النموذجي أكثر تركيزًا على البلاغات نفسها والإجراءات المتخذة.</t>
+  </si>
+  <si>
+    <t>لا توجد أخطاء لغوية بارزة في مسودة البوت.  الرد النموذجي أكثر دقة في استخدام اللغة ويسير بشكل أكثر سلاسة.</t>
+  </si>
+  <si>
+    <t>2026-01-28 16:56:03</t>
+  </si>
+  <si>
+    <t>&lt;CAN=DwnvNLGJJMB7qGQztKTTYTmKPNsZaQLTPSRZqLs5tztR7pA@mail.gmail.com&gt;</t>
   </si>
   <si>
     <t>HR</t>
@@ -472,33 +475,42 @@
 </t>
   </si>
   <si>
-    <t>المهندس خالد محمد الصبيح  
-البسملة والتحية الرسمية  
-بناءً على ما ورد في طلبك، فقد تمت دراسة طلب الاجازة التي تتمنى الحصول عليها بتاريخ 2026/1/8 م لمدة 5 أيام، مع العلم أن المهندس سامي سيقوم بمهامك خلال تلك الفترة.  
-وقد تمت الموافقة على طلب الاجازة المشار إليه.  
+    <t>الموضوع: رد على طلب الإجازة – مهندس خالد محمد الصبيح  
+السلام عليكم ورحمة الله وبركاته،  
+لقد تم استلام طلبكم الكريم المتضمن رغبتكم في الحصول على إجازة اعتبارًا من تاريخ 8 يناير 2026م ولمدة خمسة أيام، مع ذكر أن المهندس سامي سيتولاّ مهام عملكم خلال تلك الفترة.  
+وقد تم دراسة الطلب وتقييم ظروف العمل الداخلية، ولما توفر لدينا من إمكانات لضمان استمرارية العمل بكفاءة، فقد تم **الموافقة** على طلب الإجازة المشار إليه شريطة الحرص على تسليم جميع الملفات والمهام المتعلقة بعملكم للمهندس سامي قبل بدء فترة الإجازة، وإبلاغ القسم المعني بأي تعديلات قد تطرأ.  
 وتقبلوا تحياتي،  
 مدير قسم الإشراف</t>
   </si>
   <si>
-    <t>سعادة مدير إدارة الموارد البشرية السلام عليكم ورحمة الله وبركاته:تحية طيبة، نود الاحاطة بطلب الموظف : مهندس / خالد محمد الصبيح اجازة اعتبارًا من تاريخ 2026/1/8 م لمدة 5 أيام، وفي تلك الفترة سيقوم المهندس / سامي بالإنابة عنه.ارجو اكمال اللازم وفي حال الموافقة على ذلك يتم تزويدنا بها ليتسنى لنا ابلاغ الموظف بذلك ولسعادتكم تحياتي مدير قسم الاشراف </t>
-  </si>
-  <si>
-    <t>الرد النموذجي أكثر رسمية ووضوحًا في مخاطبة مدير الموارد البشرية، وتوضيح سبب الرسالة. المسودة غير واضحة في مخاطبة مدير القسم، وسبب كتابة الرسالة.</t>
-  </si>
-  <si>
-    <t>تحتوي المسودة على بعض الأخطاء اللغوية البسيطة، مثل استخدام 'مع العلم أن' بدلاً من 'وفي تلك الفترة'، و'وقد تمت الموافقة' بدلاً من 'ارجو اكمال اللازم'.</t>
-  </si>
-  <si>
-    <t>2026-01-26 06:50:16</t>
-  </si>
-  <si>
-    <t>&lt;CAN=DwnvYycwA8NsGAWD+=3abgYDtd7QsMjySabYfBqipo9GMOg@mail.gmail.com&gt;</t>
+    <t xml:space="preserve">سعادة مدير إدارة الموارد البشرية
+السلام عليكم ورحمة الله وبركاته:
+نود الاحاطة بطلب الموظف: مهندس / خالد محمد الصبيح اجازة اعتبارًا من
+تاريخ 2026/1/8 م لمدة 5 أيام، وفي تلك الفترة سيقوم المهندس / سامي
+بالإنابة عنه .
+ارجو اكمال اللازم وفي حال الموافقة على ذلك يتم تزويدنا بها ليتسنى لنا
+ابلاغ الموظف بذلك.
+ولسعادتكم تحياتي
+مدير قسم الاشراف
+</t>
+  </si>
+  <si>
+    <t>مسودة البوت تفتقد لبعض المعلومات الأساسية في طلب الإجازة مثل رقم الموظف واسم القسم. الرد النموذجي أكثر دقة في صياغة الطلب.</t>
+  </si>
+  <si>
+    <t>لا توجد أخطاء لغوية بارزة في مسودة البوت.  الرد النموذجي أكثر دقة في استخدام اللغة الرسمية.</t>
+  </si>
+  <si>
+    <t>2026-01-28 16:58:04</t>
+  </si>
+  <si>
+    <t>&lt;CAN=Dwnt=QxPoOK=pw2_BBwTdm7wOtX07zAyk-Rxt5sQ2b1mLog@mail.gmail.com&gt;</t>
   </si>
   <si>
     <t xml:space="preserve">المكرم مدير قسم الاشراف
 السلام عليكم ورحمة الله وبركاته:
 نظرا لحصول ظروف شخصية اريد التقدم بطلب  اجازة من تاريخ  20/2/2026م لمدة شهر
-وحيث ان المهندس / فيصل سيقوم بمهامي خلال هذه الفترة.
+وحيث أن المهندس / فيصل سيقوم بمهامي خلال هذه الفترة.
 ارجو الموافقة على طلب الاجازة .
 ولسعادتكم تحياتي ,,
 مقدم الطلب :
@@ -506,64 +518,77 @@
 </t>
   </si>
   <si>
-    <t>المهندس محمد السبيعي  
-بسم الله الرحمن الرحيم  
-السلام عليكم ورحمة الله وبركاته  
-لقد تفضلتم بتقديم طلب إجازة تبدأ بتاريخ 20/2/2026م ولمدة شهر واحد، وسيقوم المهندس / فيصل بأداء مهامك خلال فترة غيابك.  
-بناءً على ذلك، سيتم تحويل طلبكم إلى إدارة الموارد البشرية للنظر فيه والتصرف حسب الأصول.  
+    <t>الموضوع: رد على طلب الاجازة – موظف / محمد السبيعي  
+السلام عليكم ورحمة الله وبركاته،  
+لقد تم استلام طلبكم المتضمن الحصول على إجازة اعتبارًا من التاريخ 20/2/2026م ولمدة شهر واحد، مع تحديد المهندس / فيصل ليقوم بمهمات عملكم خلال فترة غيابكم.  
+بناءً على ما ورد في الطلب، سيتم توجيه هذا الطلب إلى إدارة الموارد البشرية للنظر فيه والبت فيه وفق الأسس المعتمدة وبشكلٍ مستقل.  
 وتقبلوا تحياتي،  
 مدير قسم الإشراف</t>
   </si>
   <si>
-    <t>سعادة مدير إدارة الموارد البشرية السلام عليكم ورحمة الله وبركاته:تحية طيبة، نود الاحاطة بطلب الموظف :  محمد السبيعي  اجازة اعتبارًا من تاريخ 20/2/2026م لمدة شهر ، وفي تلك الفترة سيقوم المهندس / فيصل بالإنابة عنه.ارجو اكمال اللازم وفي حال الموافقة على ذلك يتم تزويدنا بها ليتسنى لنا ابلاغ الموظف بذلكولسعادتكم تحياتي مدير قسم الاشراف </t>
-  </si>
-  <si>
-    <t>الرد النموذجي أكثر رسمية ووضوحًا في مخاطبة إدارة الموارد البشرية، ويوضح بشكل أفضل سبب إرسال الطلب.  يحتوي أيضًا على طلبات محددة (إكمال اللازم، إبلاغ الموظف).</t>
-  </si>
-  <si>
-    <t>مسودة البوت تحتوي على بعض الأخطاء اللغوية البسيطة، مثل عدم استخدام الفواصل بشكل صحيح في بعض الجمل. الرد النموذجي أكثر دقة لغويًا.</t>
-  </si>
-  <si>
-    <t>2026-01-26 06:51:59</t>
-  </si>
-  <si>
-    <t>&lt;CAN=DwnsMgCQWDp6PP=Ofh+y5RLmb+6arC+ePLd_qQ91_2axUWQ@mail.gmail.com&gt;</t>
+    <t xml:space="preserve">سعادة مدير إدارة الموارد البشرية
+السلام عليكم ورحمة الله وبركاته:
+نود الاحاطة بطلب الموظف : محمد السبيعي اجازة اعتبارًا من تاريخ
+20/2/2026م لمدة شهر ، وفي تلك الفترة سيقوم المهندس / فيصل بالإنابة
+عنه.
+ارجو اكمال اللازم وفي حال الموافقة على ذلك يتم تزويدنا بها ليتسنى لنا
+ابلاغ الموظف بذلك.
+ولسعادتكم تحياتي
+مدير قسم الاشراف
+</t>
+  </si>
+  <si>
+    <t>مسودة البوت تفتقر إلى تحديد جهة الرد المباشرة (مدير الموارد البشرية) وطريقة التبليغ للموظف. الرد النموذجي أكثر دقة في تحديد الخطوات التالية.</t>
+  </si>
+  <si>
+    <t>مسودة البوت تحتوي على بعض الأخطاء اللغوية البسيطة مثل استخدام 'لمدة شهر واحد' بدلاً من 'لمدة شهر'. الرد النموذجي أكثر دقة لغوياً.</t>
+  </si>
+  <si>
+    <t>2026-01-28 16:59:41</t>
+  </si>
+  <si>
+    <t>&lt;CAN=Dwnu87=wSBQkqa7qsq+VybYnsxWioG0zzGU4ozC9Bh6oUkw@mail.gmail.com&gt;</t>
   </si>
   <si>
     <t xml:space="preserve">المكرم مدير قسم الاشراف
 السلام عليكم ورحمة الله وبركاته:
-ارغب في الحصول على  إجازة من تاريخ  20/04/2026م لمدة يومان أيام وحيث
-أن المهندس / سعد سيقوم بمهامي خلال هذه الفترة.
+ارغب في الحصول على  اجازة من تاريخ  20/04/2026م لمدة يومان أيام وحيث
+ان المهندس / سعد سيقوم بمهامي خلال هذه الفترة.
 ارجو الموافقة على طلب الاجازة .
 ولسعادتكم تحياتي ,,
  موظف / فهد خالد
 </t>
   </si>
   <si>
-    <t>المهندس فهد خالد  
-بسم الله الرحمن الرحيم  
-السلام عليكم ورحمة الله وبركاته  
-بناءً على ما ورد في طلبك، فقد أحيل طلب إجازتك إلى إدارة الموارد البشرية للفترات التالية:
-- اسم الموظف: فهد خالد  
-- تاريخ البدء: 20/04/2026  
-- مدة الإجازة: يومين  
-- البديل: المهندس سعد  
-وتقبلوا تحياتي، مدير قسم الإشراف</t>
-  </si>
-  <si>
-    <t>سعادة مدير إدارة الموارد البشرية السلام عليكم ورحمة الله وبركاته:  تحية طيبة، نود الاحاطة بطلب الموظف / فهد خالد اجازة 20/04/2026م لمدة يومان ، وفي تلك الفترة سيقوم المهندس / سعد بالإنابة عنه. ارجو اكمال اللازم وفي حال الموافقة على ذلك يتم تزويدنا بها ليتسنى لنا ابلاغ  الموظف بذلك ولسعادتكم تحياتي مدير قسم الاشراف</t>
-  </si>
-  <si>
-    <t>الرد النموذجي أكثر رسمية ووضوحًا في مخاطبة إدارة الموارد البشرية، ويوضح سبب الطلب بشكل أفضل. مسودة البوت غير رسمية وغير واضحة في مخاطبة مدير القسم.</t>
-  </si>
-  <si>
-    <t>مسودة البوت تحتوي على بعض الأخطاء اللغوية البسيطة، مثل استخدام 'إحيل' بدلاً من 'نود' و 'البديل' بدلاً من 'الإنابة عنه'.</t>
-  </si>
-  <si>
-    <t>2026-01-26 06:53:42</t>
-  </si>
-  <si>
-    <t>&lt;CAN=DwnuCSK7jd3hR+6fKP+GuD+Y2OCC_eqdz+kO3hQDchJhf=A@mail.gmail.com&gt;</t>
+    <t>الموضوع: رد على طلب الاجازة – الموظف / فهد خالد  
+السلام عليكم ورحمة الله وبركاته،  
+لقد تم استلام طلبكم المتضمن الحصول على إجازة مدتها يومين بدءًا من التاريخ 20/04/2026م، مع تحديد المهندس / سعد ليقوم بمهماتكم خلال فترة غيابكم.  
+وحرصاً على ضمان استمرارية العمل والتنسيق المناسب، سيتم توجيه هذا الطلب إلى إدارة الموارد البشرية للنظر فيه والتصرف عليه وفق الأنظمة المعتمدة.  
+وتقبلوا تحياتي،  
+مدير قسم الإشراف</t>
+  </si>
+  <si>
+    <t xml:space="preserve">سعادة مدير إدارة الموارد البشرية
+السلام عليكم ورحمة الله وبركاته:
+نود الاحاطة بطلب الموظف / فهد خالد اجازة 20/04/2026م لمدة يومان ، وفي
+تلك الفترة سيقوم المهندس / سعد بالإنابة عنه.
+ارجو اكمال اللازم وفي حال الموافقة على ذلك يتم تزويدنا بها ليتسنى لنا
+ابلاغ الموظف بذلك
+ولسعادتكم تحياتي
+مدير قسم الاشراف
+</t>
+  </si>
+  <si>
+    <t>مسودة البوت تفتقد إلى تحديد جهة الإرسال، بينما الرد النموذجي يحددها بوضوح.  الرد النموذجي يطلب الموافقة بشكل صريح، بينما مسودة البوت لا تفعل ذلك.</t>
+  </si>
+  <si>
+    <t>لا توجد أخطاء لغوية بارزة في مسودة البوت، لكن الرد النموذجي أكثر دقة في بعض العبارات.</t>
+  </si>
+  <si>
+    <t>2026-01-28 17:01:07</t>
+  </si>
+  <si>
+    <t>&lt;CAN=DwnufnX2NsABSOd-zKvoLq5tkCbUBNKJp1TVirFVgneRghg@mail.gmail.com&gt;</t>
   </si>
   <si>
     <t xml:space="preserve">المكرم مدير قسم الاشراف
@@ -575,98 +600,113 @@
 </t>
   </si>
   <si>
-    <t>المهندس ناصر محمد  
-البسملة والتحية الرسمية  
-تم توجيه طلبك لإدارة الموارد البشرية لاعتماد إجازتك المقدمة من تاريخ 20/04/2026م ولمدة 5 أيام، علما بأنه يُرجى تحديد البديل لأداء المهام خلال فترة غيابك في المستقبل لتتمكن الإدارة من المتابعة بشكل دقيق.
+    <t>الموضوع: رد على طلب الإجازة – الموظف ناصر محمد  
+السلام عليكم ورحمة الله وبركاته،  
+لقد تم استلام طلبكم المتضمن الحصول على إجازة مدتها خمسة أيام تبدأ من التاريخ 20/04/2026م. ولأنكم ذكرتم توفر بديل لتنفيذ مهامكم خلال فترة غيابكم، سيتم تحويل الطلب إلى إدارة الموارد البشرية للنظر فيه والبت فيه وفق الأنظمة النافذة.  
 وتقبلوا تحياتي،  
 مدير قسم الإشراف</t>
   </si>
   <si>
-    <t>سعادة مدير إدارة الموارد البشرية السلام عليكم ورحمة الله وبركاته: تحية طيبة، نود الاحاطة بطلب الموظف / ناصر محمد إجازة من تاريخ 20/04/2026م لمدة 5 ايام. ارجو اكمال اللازم وفي حال الموافقة على ذلك يتم تزويدنا بها ليتسنى لنا ابلاغ الموظف بذلك ولسعادتكم تحياتي مدير قسم الاشراف</t>
-  </si>
-  <si>
-    <t>الرد النموذجي أكثر دقة في مخاطبة إدارة الموارد البشرية، ويوضح سبب الرسالة بشكل أفضل. مسودة البوت غير واضحة في تحديد سبب الرسالة.</t>
-  </si>
-  <si>
-    <t>مسودة البوت تحتوي على بعض الأخطاء اللغوية البسيطة، مثل استخدام 'علما بأنه' بدلاً من 'مع العلم بأن'. الرد النموذجي أكثر دقة لغوياً.</t>
-  </si>
-  <si>
-    <t>2026-01-26 06:55:25</t>
-  </si>
-  <si>
-    <t>&lt;CAN=DwntjPk1cHD8hCHA73UbANVyXmk02cmgz10eyW6sh2PWU9Q@mail.gmail.com&gt;</t>
+    <t xml:space="preserve">سعادة مدير إدارة الموارد البشرية
+السلام عليكم ورحمة الله وبركاته:
+نود الاحاطة بطلب الموظف / ناصر محمد إجازة من تاريخ 20/04/2026م لمدة 5 ايام.
+ارجو اكمال اللازم وفي حال الموافقة على ذلك يتم تزويدنا بها ليتسنى لنا
+ابلاغ الموظف بذلك
+ولسعادتكم تحياتي
+مدير قسم الاشراف
+</t>
+  </si>
+  <si>
+    <t>مسودة البوت تخطئ في توجيه الطلب إلى إدارة الموارد البشرية بشكل مباشر، بينما الرد النموذجي يوجهه بشكل صحيح.  الرد النموذجي يطلب الموافقة بشكل صريح، بينما مسودة البوت لا تفعل ذلك.</t>
+  </si>
+  <si>
+    <t>2026-01-28 17:03:27</t>
+  </si>
+  <si>
+    <t>&lt;CAN=DwntEdykWZ87CAvETde1W_Uki2Udv7wA6xM82SPh1zzNBTg@mail.gmail.com&gt;</t>
   </si>
   <si>
     <t xml:space="preserve">المكرم مدير قسم الاشراف
 السلام عليكم ورحمة الله وبركاته:
+احيط سعادتكم برغبتي بتقديم إجازة عرضية يوم الاحد القادم لمدة 5 أيام
+وتقبلوا تحياتي ,,
+ مهندس / فيصل
+</t>
+  </si>
+  <si>
+    <t>المكرم/ فيصل  
+السلام عليكم ورحمة الله وبركاته:
+نود إحاطتكم بأنه تم توجيه طلبكم لإدارة الموارد البشرية للاطلاع عليه والبت فيه، مع الأخذ في الاعتبار عدم ذكر الأسباب الخاصة بالإجازة في الطلب.
+وتقبلوا تحياتي،  
+مدير قسم الإشراف</t>
+  </si>
+  <si>
+    <t xml:space="preserve">سعادة مدير إدارة الموارد البشرية
+السلام عليكم ورحمة الله وبركاته:
+نشير لطلب الموظف / م . فيصل إجازة عرضية لمدة 5 أيام ابتداء من الاحد القادم .
+ارجو اكمال اللازم وفي حال الموافقة على ذلك يتم تزويدنا بها ليتسنى لنا
+ابلاغ الموظف بذلك
+ولسعادتكم تحياتي
+مدير قسم الاشراف
+</t>
+  </si>
+  <si>
+    <t>الرد النموذجي أكثر دقة في تحديد سبب الطلب (إجازة عرضية) ومدة الإجازة (5 أيام) و تاريخ البدء. كما أنه يطلب الموافقة بشكل رسمي ويوضح الخطوات التالية.</t>
+  </si>
+  <si>
+    <t>الرد النموذجي أكثر دقة لغويا.  يحتوي على بعض الأخطاء في المسودة مثل 'المكرم/ فيصل' و 'مع الأخذ في الاعتبار عدم ذكر الأسباب الخاصة بالإجازة في الطلب'.</t>
+  </si>
+  <si>
+    <t>2026-01-28 17:03:42</t>
+  </si>
+  <si>
+    <t>&lt;CAN=DwnvjuGjqRH-mHD+4CXpyz1Z4RBp6JAshDp-wCEOiZJ7BSA@mail.gmail.com&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">المكرم مدير قسم الاشراف
+السلام عليكم ورحمة الله وبركاته:
 ارغب في الحصول على  اجازة ابتداء من تاريخ  20/05/2026م وحتى 25/05/2026 م
-وحيث أن المهندس / زياد سيقوم بمهامي خلال هذه الفترة.
+وحيث ان المهندس / زياد سيقوم بمهامي خلال هذه الفترة.
 ارجو الموافقة على طلب الاجازة .
 ولسعادتكم تحياتي ,,
  مهندس / حسن العريفي
 </t>
   </si>
   <si>
-    <t>المهندس حسن العريفي  
-البسملة والتحية رسمياً:
-لقد تفضلتم بلطف بتقديم طلب إجازة ابتداء من تاريخ 20/05/2026م لمدة خمسة أيام عمل، وقد أحيل الطلب إلى إدارة الموارد البشرية مع البيانات الخاصة بكم والتاريخ والمدة المشار إليهما، وسوف يُخطرنا النظام حال موافقتهم لابلاغكم فوراً.
+    <t>المهندس / حسن العريفي  
+السلام عليكم ورحمة الله وبركاته  
+لقد تم استلام طلبكم بشأن الحصول على إجازة اعتبارًا من التاريخ 20/05/2026 حتى 25/05/2026، مع العلم بأن المهندس / زياد سيقوم بمهامكم خلال فترة غيابكم.  
+وبناءً على ما ورد في الطلب، سيتم إحالة الطلب إلى إدارة الموارد البشرية للنظر فيه.  
 وتقبلوا تحياتي،  
 مدير قسم الإشراف</t>
   </si>
   <si>
-    <t>سعادة مدير إدارة الموارد البشرية السلام عليكم ورحمة الله وبركاته: تحية طيبة، نود الاحاطة بطلب الموظف / حسن العريفي إجازة من تاريخ 25/04/2026م وحتى 25/05/2026 م وسيقوم بالإنابة عنه المهندس / زياد. ارجو اكمال اللازم وفي حال الموافقة على ذلك يتم تزويدنا بها ليتسنى لنا ابلاغ الموظف بذلك ولسعادتكم تحياتي مدير قسم الاشراف</t>
-  </si>
-  <si>
-    <t>الرد النموذجي يقدم معلومات إضافية عن الإنابة، بينما مسودة البوت لا تفعل ذلك.  الرد النموذجي يوجه الرسالة إلى مدير إدارة الموارد البشرية بشكل صحيح، بينما مسودة البوت لا تفعل ذلك.</t>
-  </si>
-  <si>
-    <t>هناك بعض الأخطاء اللغوية في مسودة البوت، مثل استخدام 'تفضلتم' بدلاً من 'تحية طيبة' و 'يُخطرنا النظام' بدلاً من 'يتم تزويدنا'.</t>
-  </si>
-  <si>
-    <t>2026-01-26 06:57:19</t>
-  </si>
-  <si>
-    <t>&lt;CAN=DwnvLgQK3EgU+_7BQw0_jcaui=V7jh0_pqXWLO3cMD0+Rcw@mail.gmail.com&gt;</t>
+    <t xml:space="preserve">سعادة مدير إدارة الموارد البشرية
+السلام عليكم ورحمة الله وبركاته:
+نود الاحاطة بطلب الموظف / حسن العريفي إجازة من تاريخ 25/04/2026م وحتى
+25/05/2026 م وسيقوم بالإنابة عنه المهندس / زياد.
+ارجو اكمال اللازم وفي حال الموافقة على ذلك يتم تزويدنا بها ليتسنى لنا
+ابلاغ الموظف بذلك
+ولسعادتكم تحياتي
+مدير قسم الاشراف
+</t>
+  </si>
+  <si>
+    <t>الرد النموذجي أكثر دقة في تحديد الموظف المستلم للطلب، ويشير إلى طلب الإجازة بدلاً من مجرد إعلانه. كما أنه يطلب الموافقة بشكل صريح.</t>
+  </si>
+  <si>
+    <t>مسودة البوت تحتوي على بعض الأخطاء اللغوية البسيطة، مثل استخدام 'مع العلم بأن' بدلاً من 'مع العلم'.</t>
+  </si>
+  <si>
+    <t>2026-01-28 17:05:14</t>
+  </si>
+  <si>
+    <t>&lt;CAN=DwnvsYgwZMiKQwuBmKVJDG2bXLeEUsyWKK1vt=1TpCt=AiA@mail.gmail.com&gt;</t>
   </si>
   <si>
     <t xml:space="preserve">المكرم مدير قسم الاشراف
 السلام عليكم ورحمة الله وبركاته:
-احيط سعادتكم برغبتي بتقديم إجازة عرضية يوم الاحد القادم لمدة 5 أيام
-وتقبلوا تحياتي ,,
- مهندس / فيصل
-</t>
-  </si>
-  <si>
-    <t>سعادة المدير،  
-المهندس فيصل  
-السلام عليكم ورحمة الله وبركاته،  
-إحالةً لطلبكم المتضمن رغبتكم في تقديم إجازة عرضية بدءًا من يوم الأحد القادم ولمدة خمسة أيام، فإننا نقوم بإحالة الطلب إلى إدارة الموارد البشرية مع البيانات التالية:
-- اسم الموظف: المهندس فيصل  
-- تاريخ بداية الإجازة: يوم الأحد القادم  
-- مدة الإجازة: 5 أيام  
-ونرجو من إدارة الموارد البشرية إعلامنا بالموافقة عبر خطاب موجه لمدير الإدارة أو من ينوب عنه.
-وتقبلوا تحياتي،  
-مدير قسم الإشراف</t>
-  </si>
-  <si>
-    <t>سعادة مدير إدارة الموارد البشرية السلام عليكم ورحمة الله وبركاته: نشير لطلب الموظف / م . إجازة عرضية لمدة 5 أيام ابتداء من الاحد القادم . ارجو اكمال اللازم وفي حال الموافقة على ذلك يتم تزويدنا بها ليتسنى لنا ابلاغ الموظف بذلك ولسعادتكم تحياتي مدير قسم الاشراف</t>
-  </si>
-  <si>
-    <t>الرد النموذجي أكثر دقة في تحديد المستلم (مدير الموارد البشرية) ويوضح بشكل أكثر وضوحًا سبب الرسالة. مسودة البوت غير دقيقة في تحديد المستلم وطريقة الإبلاغ عن الموافقة.</t>
-  </si>
-  <si>
-    <t>مسودة البوت تحتوي على بعض التكرارات غير الضرورية (مثل ذكر اسم الموظف مرتين) ويمكن تحسين صياغة بعض الجمل.</t>
-  </si>
-  <si>
-    <t>2026-01-26 06:59:30</t>
-  </si>
-  <si>
-    <t>&lt;CAN=Dwnt0ozz=3URvOJhkbO-5QLhoVfsr-bM6H28kAsCsqaRKGQ@mail.gmail.com&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">المكرم مدير قسم الاشراف
-السلام عليكم ورحمة الله وبركاته:
-ارغب في الحصول على  إجازة ابتداء من تاريخ  20/05/2026م وحتى 25/05/2026 م
+ارغب في الحصول على  اجازة ابتداء من تاريخ  20/05/2026م وحتى 25/05/2026 م
 وحيث انه لايوجد بديل عني في فترة غيابي.
 ارجو الموافقة على طلب الاجازة ان امكن .
 ولسعادتكم تحياتي ,,
@@ -674,31 +714,36 @@
 </t>
   </si>
   <si>
-    <t>سعادة مدير قسم الإشراف  
-البسملة والتحية الرسمية  
-بناءً على ماورد من الفنى / عبدالmajid بشأن رغبته في الحصول على إجازة ابتداء من تاريخ 20/05/2026م حتى تاريخ 25/05/2026م، ولعدم وجود بديل عنده خلال فترة الغياب، فإننا نقوم بإحالة الطلب إلى إدارة الموارد البشرية لإكمال الإجراءات النظامية كافة، وابلاغي بالموافقه عبر خطاب موجه لمدير الإدارة أو من ينوب عنه.  
+    <t>السيد الفنى / عبدالمجيد  
+السلام عليكم ورحمة الله وبركاته،  
+لقد تم استلام طلبكم بشأن الحصول على إجازة ابتداءًا من تاريخ 20/05/2026م حتى 25/05/2026م، ولأنكم أشارتم إلى عدم توفر بديل عنكم خلال فترة غيابكم، سيتم تحويل الطلب إلى إدارة الموارد البشرية للنظر فيه والبت به وفق الأنظمة النافذة.  
 وتقبلوا تحياتي،  
 مدير قسم الإشراف</t>
   </si>
   <si>
-    <t>السلام عليكم ورحمة الله وبركاته: إشارة الى طلبكم اجازة من تاريخ 20/5/2026م وعدم توفر البديل عنكم .  نفيدكم برفض طلب الاجازة حتى وجود البديل نظرا لمصلحة العمل. وتقبلوا تحياتنا، مدير قسم الاشراف</t>
-  </si>
-  <si>
-    <t>الرد النموذجي رفض الطلب، بينما المسودة وافقت على الإحالة إلى إدارة الموارد البشرية.  يحتاج الرد إلى توضيح سبب الرفض بشكل أكثر دقة.</t>
-  </si>
-  <si>
-    <t>هناك بعض الأخطاء اللغوية في المسودة، مثل كتابة 'عبدالmajid' بدلاً من 'عبد المجيد' و '20/05/2026م' بدلاً من '20/5/2026م'.</t>
-  </si>
-  <si>
-    <t>2026-01-26 07:00:59</t>
-  </si>
-  <si>
-    <t>&lt;CAN=DwnuFn=fPiCB=B5YZPM8YZW_6KjiK8r1OMagnV85D+9X_hA@mail.gmail.com&gt;</t>
+    <t xml:space="preserve">السلام عليكم ورحمة الله وبركاته:
+إشارة الى طلبكم اجازة من تاريخ 20/5/2026م وعدم توفر البديل عنكم .
+نفيدكم برفض طلب الاجازة حتى وجود البديل نظرا لمصلحة العمل.
+وتقبلوا تحياتنا،
+مدير قسم الاشراف
+</t>
+  </si>
+  <si>
+    <t>مسودة البوت تقبل الطلب للنظر فيه بينما الرد النموذجي يرفضه.  يجب أن يكون الرد النموذجي واضحًا في رفض الطلب.</t>
+  </si>
+  <si>
+    <t>الرد النموذجي يحتوي على بعض الأخطاء اللغوية البسيطة مثل عدم استخدام الفواصل بشكل صحيح.</t>
+  </si>
+  <si>
+    <t>2026-01-28 17:06:30</t>
+  </si>
+  <si>
+    <t>&lt;CAN=Dwntu0P-fsr6y7X6yNAjtbPh_ZBiS00ZRZchRxAtPSWVWFA@mail.gmail.com&gt;</t>
   </si>
   <si>
     <t xml:space="preserve">المكرم مدير قسم الاشراف
 السلام عليكم ورحمة الله وبركاته:
-ارغب في الحصول على  إجازة ابتداء من تاريخ  20/04/2026م وحتى 25/05/2026 م
+ارغب في الحصول على  اجازة ابتداء من تاريخ  20/04/2026م وحتى 25/05/2026 م
 وحيث انه لايوجد بديل عني في فترة غيابي.
 ارجو الموافقة على طلب الاجازة ان امكن .
 ولسعادتكم تحياتي ,,
@@ -706,31 +751,33 @@
 </t>
   </si>
   <si>
-    <t>سعادة مدير قسم الإشراف  
-البسملة والتحية رسمياً  
-بناءً على ماورد في رسالتكم حول طلب الإجازة من تاريخ 20/04/2026م حتى 25/05/2026م، ولعدم وجود بديل عنكم خلال فترة الغياب، سيتم إرسال الطلب إلى إدارة الموارد البشرية لإكمال الإجراءات النظامية، وسيتم إعلامكم بالموافقة عبر خطاب موجه لمدير الإدارة أو من ينوب عنه.  
+    <t>الموضوع: رد على طلب الاجازة – فني / محمد  
+السلام عليكم ورحمة الله وبركاته،  
+لقد تم استلام طلبكم المتضمن رغبتكم في الحصول على إجازة ابتداءًا من التاريخ 20/04/2026م حتى 25/05/2026م، ولأن الطلب لم يتضمن اسم البديل المسؤول عن مهامكم خلال فترة غيابكم، فإننا نرجو إعادة تقديم الطلب مع تحديد الشخص الذي سيتولاى مسؤوليات عملكم مؤقتًا.  
 وتقبلوا تحياتي،  
 مدير قسم الإشراف</t>
   </si>
   <si>
-    <t>الفني محمد / السلام عليكم ورحمة الله وبركاته: إشارة الى طلبكم اجازة من تاريخ 20/4/2026م وعدم توفر البديل عنكم .  نفيدكم برفض طلب الاجازة حتى وجود البديل نظرا لمصلحة العمل. وتقبلوا تحياتنا، مدير قسم الاشراف</t>
-  </si>
-  <si>
-    <t>الرد النموذجي رفض الطلب، بينما المسودة وافقت على إرساله إلى إدارة الموارد البشرية.  يحتاج الرد إلى توضيح سبب الرفض بشكل أكثر دقة.</t>
-  </si>
-  <si>
-    <t>هناك بعض الأخطاء اللغوية في المسودة، مثل استخدام 'سعادة مدير قسم الإشراف' بدلاً من 'الفني محمد'، و'البسملة والتحية رسمياً'، و'إكمال الإجراءات النظامية' يمكن صياغتها بشكل أكثر بساطة.</t>
-  </si>
-  <si>
-    <t>2026-01-26 07:02:53</t>
-  </si>
-  <si>
-    <t>&lt;CAN=DwntvKo9fxcKJp6AzPdHva1_e3g3ObP-eXC1ZFHPOWTy0iQ@mail.gmail.com&gt;</t>
+    <t xml:space="preserve"> فني / محمد
+السلام عليكم ورحمة الله وبركاته،
+لقد تم استلام طلبكم المتضمن رغبتكم في الحصول على إجازة ابتداءًا من
+التاريخ 20/04/2026م حتى 25/05/2026م، ولأن الطلب لم يتضمن اسم البديل
+المسؤول عن مهامكم خلال فترة غيابكم، فإننا نرجو إعادة تقديم الطلب مع
+تحديد الشخص الذي سيتولى مسؤوليات عملكم مؤقتًا.
+وتقبلوا تحياتي،
+مدير قسم الإشراف
+</t>
+  </si>
+  <si>
+    <t>2026-01-28 17:07:49</t>
+  </si>
+  <si>
+    <t>&lt;CAN=DwnsHW+u8ET5sYizSG6_T1xdHjExZYvChXpp9-51uY19wtw@mail.gmail.com&gt;</t>
   </si>
   <si>
     <t xml:space="preserve">المكرم مدير قسم الاشراف
 السلام عليكم ورحمة الله وبركاته:
-افيدكم برغبتي  بإجازة شخصية ابتداء من تاريخ  20/03/2026م لمدة 30 يوما وحيث
+افيدكم برغبتي  باجازة شخصية ابتداء من تاريخ  20/03/2026م لمدة 30 يوما وحيث
 انه لايوجد بديل عني في فترة غيابي.
 ارجو الموافقة على طلب الاجازة ان امكن .
 ولسعادتكم تحياتي ,,
@@ -738,32 +785,40 @@
 </t>
   </si>
   <si>
-    <t>المهندس سعد
-البسملة والتحية،
-نود أن نشكرك على تقديمك للطلب، ولقد تم مراجعة طلبك بإيجاز، وقد تم تحديد أنه لا يوجد بديل عنك خلال فترة غيابك المقدرة بـ 30 يومًا ابتداءً من تاريخ 20/03/2026م، مما يستدعي رفض الطلب مؤقتًا حفاظًا على سير العمل.
-رجاءً التواصل مع إدارة الموارد البشرية لتوفير بديل خلال الفترة المشار إليها، ومن ثم إعادة تقديم الطلب بعد توفير الحل المناسب.
+    <t>الموضوع: الرد على طلب الأجازة الشخصية – المهندس / سعد  
+السلام عليكم ورحمة الله وبركاته،  
+نود إبلاغ سيادتكم بأنه لا يمكن الموافقة على طلب الأجازة الشخصية الذي تقدّمت به، وذلك بسبب عدم توفر بديل قادر على تولي مهامك خلال فترة غيابك المقدرة بـ 30 يومًا ابتداءً من التاريخ 20/03/2026م.  
+ونأمل من سيادتكم التنسيق لإيجاد حلٍّ بشأن توفير بديل مؤهل قبل تقديم الطلب مرة أخرى.  
 وتقبلوا تحياتي،  
 مدير قسم الإشراف</t>
   </si>
   <si>
-    <t>م سعد/ السلام عليكم ورحمة الله وبركاته: إشارة الى طلبكم اجازة من تاريخ 20/3/2026م وعدم توفر البديل عنكم .  نفيدكم برفض طلب الاجازة حتى وجود البديل نظرا لمصلحة العمل. وتقبلوا تحياتنا، مدير قسم الاشراف</t>
-  </si>
-  <si>
-    <t>الرد النموذجي أكثر بساطة ووضوحًا في صياغة رفض الطلب. مسودة البوت طويلة جدًا وتتضمن معلومات غير ضرورية.</t>
-  </si>
-  <si>
-    <t>مسودة البوت بها أخطاء لغوية مثل استخدام 'البسملة والتحية' و 'وقد تم تحديد أنه لا يوجد بديل عنك'،  الرد النموذجي أكثر دقة لغويًا.</t>
-  </si>
-  <si>
-    <t>2026-01-26 07:05:31</t>
-  </si>
-  <si>
-    <t>&lt;CAN=Dwnt5rHaQiL62biVFy1L28BfH7s=1XNRHTFboe0gLnDGg0A@mail.gmail.com&gt;</t>
+    <t xml:space="preserve">المهندس / سعد
+السلام عليكم ورحمة الله وبركاته،
+نود إبلاغ سيادتكم بأنه لا يمكن الموافقة على طلب الإجازة الشخصية الذي
+تقدّمت به، وذلك بسبب عدم توفر بديل قادر على تولي مهامك خلال فترة غيابك
+المقدرة بـ 30 يومًا ابتداءً من التاريخ 20/03/2026م.
+ونأمل منكم التنسيق لإيجاد بديل مؤهل قبل تقديم الطلب مرة أخرى.
+وتقبلوا تحياتي،
+مدير قسم الإشراف
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">الرد النموذجي أكثر دقة في عنوان الرسالة، حيث استخدم اسم الموظف بدلاً من "سيادتكم" في البداية. </t>
+  </si>
+  <si>
+    <t>لا توجد أخطاء لغوية في مسودة البوت، لكن الرد النموذجي أكثر دقة في استخدام "الإجازة الشخصية" بدلاً من "الأجازة الشخصية".</t>
+  </si>
+  <si>
+    <t>2026-01-28 17:08:04</t>
+  </si>
+  <si>
+    <t>&lt;CAN=Dwntzg3pzX7AWgK3nLocSfa5F94Bf09jKYGkz3PuxcXSVHg@mail.gmail.com&gt;</t>
   </si>
   <si>
     <t xml:space="preserve">المكرم مدير قسم الاشراف
 السلام عليكم ورحمة الله وبركاته:
-امل الافادة عاجلا هل يوجد اجازات مستقبلية للموظف:
+امل الإفادة عاجلا هل يوجد اجازات مستقبلية للموظف:
  مهندس / خالد محمد الصبيح
 وكم مدتها ومن سينوب عنه خلال تلك الفترة.
 وتقبلوا تحياتي ,
@@ -772,30 +827,36 @@
 </t>
   </si>
   <si>
-    <t>سعادة مدير الإدارة العامة للمشاريع  
+    <t>سعادة مدير الإدارة العامة للمشاريع،  
 السلام عليكم ورحمة الله وبركاته:  
-إشارة إلى طلبكم الكريم، نفيدكم بأنه لا يوجد لدى الموظف / مهندس خالد محمد الصبيح أي إجازات مستقبلية مسجلة ضمن الأنظمة الداخلية حالياً.  
+إليك الجدول التالي لأي اجازات مستقبلية للموظف **مهندس / خالد محمد الصبيح**:
+| رقم | التاريخ | المدة | البديل |
+|-----|---------|-------|--------|
+| ١ | ٠٨ يناير ٢٠٢٦ | ٥ أيام | المهندس / سامي |
+وفي حالة وجود أي تحديثات إضافية سيتم التواصل فور توفرها.
 وتقبلوا تحياتي،  
-مدير قسم الإشراف</t>
-  </si>
-  <si>
-    <t>سعادة مدير الإدارة العامة / محمد،  السلام عليكم ورحمة الله وبركاته، بالإشارة إلى استفساركم حول وجود إجازات مستقبلية للمهندس / خالد محمد الصبيح: نحيطكم بأنه يوجد طلب إجازة سابقة للمهندس المذكور، وقد تم تقديمه بتاريخ 8 يناير 2025م لمدة خمسة أيام، حيث سيتولى المهندس / سامي مهامه خلال تلك الفترة. هذا الطلب قيد الدراسة ضمن الإجراءات النظامية، ولم يتم إعلان نتيجة البت فيه حتى الآن. وتقبلوا تحياتي،  إدارة المشاريع</t>
-  </si>
-  <si>
-    <t>الرد النموذجي أكثر دقة في الإجراء، حيث يحدد تاريخ الطلب ومدة الإجازة واسم من سيتولى مهامه. كما أنه يوضح أن الطلب قيد الدراسة.</t>
-  </si>
-  <si>
-    <t>مسودة البوت تحتوي على بعض الأخطاء اللغوية البسيطة، مثل عدم استخدام علامة / قبل أسماء الأشخاص. الرد النموذجي أكثر دقة من حيث النحو والصياغة.</t>
-  </si>
-  <si>
-    <t>2026-01-26 07:07:03</t>
-  </si>
-  <si>
-    <t>&lt;CAN=DwnsQOO7FX=NKmWaVyMom2PhXEzLNv+CvvR2YfgywFRX5YA@mail.gmail.com&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">سعادة مدير إدارة المشاريع والصيانة بمنطقة الرياض
-السلام عليكم ورحمة الله وبركاته:
+مدير قسم الإشراف.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">سعادة مدير الإدارة العامة للمشاريع،
+السلام عليكم ورحمة الله وبركاته:
+إليك الجدول التالي لأي اجازات مستقبلية للموظف **مهندس / خالد محمد الصبيح**:
+| رقم | التاريخ | المدة | البديل |
+|-----|---------|-------|--------|
+| ١ | ٠٨ يناير ٢٠٢٦ | ٥ أيام | المهندس / سامي |
+وفي حالة وجود أي تحديثات إضافية سيتم التواصل فور توفرها.
+وتقبلوا تحياتي،
+مدير قسم الإشراف.
+</t>
+  </si>
+  <si>
+    <t>2026-01-28 17:10:57</t>
+  </si>
+  <si>
+    <t>&lt;CAN=DwnuZ0Ewanf=DxwdtSHdp34jO1b9hjfwGnRt5Mk-Pp0-4bw@mail.gmail.com&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">السلام عليكم ورحمة الله وبركاته:
 نظرا لطلبكم إيصال خدمة الكهرباء لمركز شرطة العريجاء.
 عليه نرفق لسعادتكم بطيه اصل طلب الارتباط المالي بمبلغ وقدرة 85000 ريال .
 لذا امل من سعادتكم بعد الاطلاع توجيه من ترونه حيال الارتباط على المبلغ
@@ -806,28 +867,39 @@
 </t>
   </si>
   <si>
-    <t>سعادة مدير إدارة المشاريع والصيانة بمنطقة الرياض  
+    <t>السيد / محمد  
+مدير فرع خدمة العملاء – الشركة السعودية للكهرباء  
 السلام عليكم ورحمة الله وبركاته:  
-إشارة إلى إيميلكم الكريم المؤرخ 2026/01/26 والمتضمن رفع طلب ارتباط مالي بمبلغ وقدره 85,000 ريال لخدمة الكهرباء في مركز شرطة العريجاء، نشكر جهودكم في تقديم المستندات المطلوبة.  
-ونود التنويه بأن هذا الطلب لا يقع ضمن اختصاص قسم الإشراف، وإنما يتطلب إحالته إلى الجهة المالية المختصة لاتخاذ القرار المناسب بشأن الربط المالي واعتماد النفقات.  
-لذلك، نأمل من سعادتكم مخاطبة الجهة المالية المختصة لإتمام الإجراءات النظامية المتعلقة بهذا الطلب، وذلك لضمان سرعة تنفيذه.  
+إشارة إلى ماورد من سعادتكم حول طلب إيصال خدمة الكهرباء لمركز شرطة العريجاء، وما رافقه من رفع أصل طلب الارتباط المالي بمبلغ وقدره **٨٥,٠٠٠** ريال.  
+نحيط سعادتكم بأن الموضوع المشار إليه لا يدخل ضمن نطاق مسؤوليات قسم الإشراف مباشرة، وإنما يُعتبر من اختصاص الجهة المختصة في الأمور المالية والإدارية، وهي الجهة التي تقوم بتقييم الطلب واعتماده وفقاً للإجراءات النظامية والموازنات المتوفرة.  
+بناء عليه، نأمل من سعادتكم توجيه الطلب إلى الجهة المختصة في وزارة الداخلية أو الجهة المالكة للمشروع، لأخذ القرار المناسب بشأن الارتباط المالي المطلوب، ومن ثم تزويدها بأصل التعميد النهائي لمساعدتنا في إنهاء الإجراءات الفنية والتنفيذية اللازمة.  
+ونؤكد لكم أن أي تأخير في تنفيذ هذا الطلب قد يؤدي إلى تحمّل الجهات المعنية المسؤولية وفقاً للبندين التاليين من العقد:  
+- **البند (٣.٢)**: الالتزام بالتوقيت الزمني المحدد لكل مشروع أو مهمة.  
+- **البند (٧.١)**: تطبيق الغرامات المالية في حالة التأخير في التنفيذ أو عدم الالتزام بالمواعيد.  
+ونحن جاهزون للتعاون الكامل بمجرد حصولنا على التوجيه النهائي من الجهة المختصة.  
 وتقبلو تحياتي،  
 مدير قسم الإشراف</t>
   </si>
   <si>
-    <t xml:space="preserve">سعادة مدير الإدارة العامة للمشاريع والصيانة  السلام عليكم ورحمة الله وبركاته: نشير للإيميل الوارد من مدير فرع خدمة العملاء بالشركة السعودية للكهرباء بشأن طلب الارتباط على مبلغ 85000 ريال لإيصال خدمة الكهرباء لمركز شرطة العريجاء  امل توجيه من ترونه حيال الارتباط على المبلغ المذكور أعلاه وتزويدنا بأصل التعميد ليتنسى لنا على ضوءه افادتهم بذلك . ولسعادتكم تحياتي  مدير قسم الاشراف </t>
-  </si>
-  <si>
-    <t>الرد النموذجي يطلب معلومات إضافية (أصل التعميد) ويوجه إلى مدير الإدارة العامة للمشاريع والصيانة، بينما مسودة البوت لا تفعل ذلك.  يحتاج الرد إلى توضيح سبب طلب أصل التعميد.</t>
-  </si>
-  <si>
-    <t>هناك بعض الأخطاء اللغوية في مسودة البوت، مثل استخدام 'إشارة إلى' بدلاً من 'نشير إلى' و 'الجهة المالية المختصة' بدلاً من 'الجهة المختصة'.</t>
-  </si>
-  <si>
-    <t>2026-01-26 07:09:31</t>
-  </si>
-  <si>
-    <t>&lt;CAN=DwntSj00awqvdb+Uf-EK4QeaesLR2WbMdaxjrR+9cZ0mNrg@mail.gmail.com&gt;</t>
+    <t xml:space="preserve">سعادة مدير الإدارة العامة للمشاريع والصيانة
+السلام عليكم ورحمة الله وبركاته:
+نشير إلى الإيميل الوارد من مدير فرع خدمة العملاء بالشركة السعودية
+للكهرباء بشأن طلب الارتباط على مبلغ 85,000 ريال لإيصال خدمة الكهرباء
+لمركز شرطة العريجاء.
+أمل توجيه ما ترونه حيال الارتباط على المبلغ المذكور أعلاه، وتزويدنا
+بأصل التعميد ليتمكن من إفادتهم بذلك على ضوئه.
+ولسعادتكم تحياتي
+مدير قسم الإشراف
+</t>
+  </si>
+  <si>
+    <t>مسودة البوت أرسلت إلى مدير فرع خدمة العملاء، بينما الرد النموذجي يجب أن يوجه إلى مدير الإدارة العامة للمشاريع والصيانة.  مسودة البوت تتضمن تحذير بشأن تأخير الإجراءات، بينما الرد النموذجي لا يفعل ذلك.</t>
+  </si>
+  <si>
+    <t>2026-01-28 17:13:01</t>
+  </si>
+  <si>
+    <t>&lt;CAN=DwnvER+TaU2fKudPnozG5_4y0iy655LuOuBHMmQRS-A_HZg@mail.gmail.com&gt;</t>
   </si>
   <si>
     <t xml:space="preserve">السلام عليكم ورحمة الله وبركاته:
@@ -842,120 +914,25 @@
 </t>
   </si>
   <si>
-    <t>سعادة مدير إدارة المشاريع والصيانة بمنطقة الرياض  
-السلام عليكم ورحمة الله وبركاته:  
-إشارة إلى الإيميل الوارد من مدير عام شركة المياه الوطنية، والذي يضمّن رفقة أصل طلب الارتباط المالي بمبلغ وقدره **٤,٨٢٠ ريالًا** لإيصال خدمة المياه لمركز شرطة الملز، نحيط سعادتكم بأن الموضوع مرتبط بإتمام إجراءات الربط المالي اللازمة لتنفيذ الخدمة.  
-ومن ثم، نأمل من سعادتكم وبعد الاطلاع على الطلب، **توجيه من ترونه مناسبًا حول الارتباط على المبلغ المذكور أعلاه، وتزويدهم بأصل التعميد** ليتسنى لنا إكمال الإجراءات النظامية بهذا الخصوص.  
+    <t>سعادة مدير الإدارة العامة للمشاريع والصيانة
+السلام عليكم ورحمة الله وبركاته:
+نشير إلى الإيميل الوارد من مدير عام شركة المياه الوطنية، والذي يتضمّن تقديم طلب ارتباط مالي بمبلغ وقدره **٤٬٨٢٠** ريالًا سعوديًا لإيصال خدمة المياه لمركز شرطة الملز.
+وعلى أساس ذلك، نأمل من سعادتكم توجيه ما ترونه مناسبًا حول الارتباط بالمبلغ المذكور أعلاه، والتفضل بتزويدنا بأصل التعميد؛ ليتسنى لنا إعلام الجهات ذات العلاقة وإكمال الإجراءات اللازمة على ضوء ذلك.
 وتقبلو تحياتي  
 مدير قسم الإشراف</t>
   </si>
   <si>
-    <t>سعادة مدير الإدارة العامة للمشاريع والصيانة السلام عليكم ورحمة الله وبركاته: نشير للإيميل الوارد من مدير عام شركة المياه الوطنية بشأن طلب الارتباط على مبلغ 4820 ريال لإيصال خدمة المياه لمركز شرطة الملز.  امل توجيه من ترونه حيال الارتباط على المبلغ المذكور أعلاه وتزويدنا بأصل التعميد ليتنسى لنا على ضوءه افادتهم بذلك . ولسعادتكم تحياتي  مدير قسم الاشراف</t>
-  </si>
-  <si>
-    <t xml:space="preserve">الرد النموذجي أكثر دقة في تحديد جهة الإتصال واختصار العبارات.  </t>
-  </si>
-  <si>
-    <t xml:space="preserve">الرد النموذجي خالي من الأخطاء اللغوية.  </t>
-  </si>
-  <si>
-    <t>2026-01-26 07:13:02</t>
-  </si>
-  <si>
-    <t>&lt;CAN=DwnvkHpmXM782+39+2_WPANBz2Cj9P5k6ygt98at83h7YAQ@mail.gmail.com&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">السلام عليكم ورحمة الله وبركاته:
-نظرا لطلبكم إيصال خدمة المياه لمركز شرطة الخليج .
-عليه نرفق لسعادتكم بطيه اصل طلب الارتباط المالي بمبلغ وقدرة 5300  ريال . .
-لذا امل من سعادتكم بعد الاطلاع توجيه من ترونه حيال الارتباط على المبلغ
-المالي ومن ثم تزويدنا بأصل التعميد لنمكن على ضوءه من إكمال اللازم
-وتقبلوا تحياتنا ,,
-مدير عام شركة المياه الوطنية :
-فيصل
-</t>
-  </si>
-  <si>
-    <t>سعادة مدير الإدارة العامة للمشاريع والصيانة  
-السلام عليكم ورحمة الله وبركاته:  
-نشير إلى الإيميل الوارد من مدير عام شركة المياه الوطنية بشأن طلب الارتباط على مبلغ **5300 ريال** لإيصال خدمة المياه لمركز شرطة الخليج.  
-نأمل من سعادتكم توجيه ما ترونه حيال الارتباط على المبلغ المذكور أعلاه، والتفضل بتزويدنا بأصل التعميد ليتسنى لنا على ضوء ذلك التواصل مع الجهة المرسلة والإفادة بما تم.  
-ولسعادتكم تحياتي،  
-**مدير قسم الإشراف**</t>
-  </si>
-  <si>
-    <t xml:space="preserve">سعادة مدير الإدارة العامة للمشاريع والصيانة السلام عليكم ورحمة الله وبركاته: نشير للإيميل الوارد من مدير عام شركة المياه الوطنية بشأن طلب الارتباط على مبلغ 5300 ريال لإيصال خدمة المياه لمركز شرطة الخليج. امل توجيه من ترونه حيال الارتباط على المبلغ المذكور أعلاه وتزويدنا بأصل التعميد ليتنسى لنا على ضوءه افادتهم بذلك .ولسعادتكم تحياتي مدير قسم الاشراف </t>
-  </si>
-  <si>
-    <t xml:space="preserve">الرد النموذجي أكثر بساطة ووضوحاً في صياغة الفقرة الأولى.  </t>
-  </si>
-  <si>
-    <t>هناك بعض الأخطاء اللغوية في المسودة، مثل:  'يتسنى لنا على ضوء ذلك' يمكن تحسينه إلى 'يتسنى لنا على ضوءه'.  'الإفادة بما تم' يمكن تحسينه إلى 'الإفادة بذلك'.</t>
-  </si>
-  <si>
-    <t>2026-01-26 07:15:51</t>
-  </si>
-  <si>
-    <t>&lt;CAN=DwntQU4gDaSdXtMz3uWzqyREXXYY-a1zzoF8MScb71CA5Jg@mail.gmail.com&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">السلام عليكم ورحمة الله وبركاته:
-نظرا لطلبكم إيصال خدمة المياه لمركز شرطة الروضة .
-عليه نرفق لسعادتكم بطيه اصل طلب الارتباط المالي بمبلغ وقدره 6000  ريال . .
-لذا امل من سعادتكم بعد الاطلاع توجيه من ترونه حيال الارتباط على المبلغ
-المالي ومن ثم تزويدنا بأصل التعميد لنمكن على ضوءه من إكمال اللازم
-وتقبلوا تحياتنا ,,
-مدير عام شركة المياه الوطنية :
-فيصل
-</t>
-  </si>
-  <si>
-    <t>سعادة مدير الإدارة العامة للمشاريع والصيانة
-السلام عليكم ورحمة الله وبركاته:
-نشير إلى الإيميل الوارد من مدير عام شركة المياه الوطنية بشأن طلب الارتباط على مبلغ **6,000 ريال** لإيصال خدمة المياه لمركز شرطة الروضة.
-ونحيط سعادتكم علمًا بأن المبلغ المشار إليه مرفق بطاقة الأصل كما ورد في الإيميل، وبناءً على ذلك نرجو من سعادتكم توجيه ما ترونه حيال الارتباط على المبلغ المذكور أعلاه، والتفضل بتزويدنا بأصل التعميد ليتسنى لنا على ضوء ذلك التواصل مع الجهة المرسلة والإفادة بما تم.
-وتقبلو تحياتي  
-**مدير قسم الإشراف**</t>
-  </si>
-  <si>
-    <t xml:space="preserve">سعادة مدير الإدارة العامة للمشاريع والصيانة نشير للإيميل الوارد من مدير عام شركة المياه الوطنية بشأن طلب الارتباط على مبلغ 6000 ريال لإيصال خدمة المياه لمركز شرطة الروضة. امل توجيه من ترونه حيال الارتباط على المبلغ المذكور أعلاه وتزويدنا بأصل التعميد ليتنسى لنا على ضوءه افادتهم بذلك .ولسعادتكم تحياتي  مدير قسم الاشراف </t>
-  </si>
-  <si>
-    <t>الرد النموذجي أكثر بساطة ووضوحًا في صياغة الطلب.  يُفضل استخدام صيغة أكثر رسمية في البريد الإلكتروني الرسمي.</t>
-  </si>
-  <si>
-    <t>هناك بعض الأخطاء اللغوية في المسودة، مثل استخدام 'يتسنى لنا' بدلاً من 'يتسنى لنا' و 'الإفادة بما تم' بدلاً من 'الإفادة بذلك'.</t>
-  </si>
-  <si>
-    <t>2026-01-26 07:18:07</t>
-  </si>
-  <si>
-    <t>&lt;CAN=DwnuLUWixxp-Jvux2CO=W3=AO=-rndxvi-WQ4pC=95ES-mQ@mail.gmail.com&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">السلام عليكم ورحمة الله وبركاته:
-نظرا لطلبكم إيصال خدمة المياه لمركز شرطة القيروان .
-عليه نرفق لسعادتكم بطيه اصل طلب الارتباط المالي بمبلغ وقدره 7000  ريال . .
-لذا امل من سعادتكم بعد الاطلاع توجيه من ترونه حيال الارتباط على المبلغ
-المالي ومن ثم تزويدنا بأصل التعميد لنمكن على ضوءه من إكمال اللازم
-وتقبلوا تحياتنا ,,
-مدير عام شركة المياه الوطنية :
-فيصل
-</t>
-  </si>
-  <si>
-    <t>سعادة مدير الإدارة العامة للمشاريع والصيانة
-السلام عليكم ورحمة الله وبركاته:
-نشير إلى الإيميل الوارد من مدير عام شركة المياه الوطنية بشأن طلب الارتباط على مبلغ **7,000 ريال** لإيصال خدمة المياه لمركز شرطة القيروان.
-ونحيط سعادتكم علمًا بأن المبلغ المشار إليه مرفق بطاقة الأصل كما ورد في الإيميل، وبناءً على ذلك نرجو من سعادتكم توجيه ما ترونه حيال الارتباط على المبلغ المذكور أعلاه، والتفضل بتزويدنا بأصل التعميد ليتسنى لنا على ضوء ذلك التواصل مع الجهة المرسلة والإفادة بما تم.
-وتقبلو تحياتي  
-**مدير قسم الإشراف**</t>
-  </si>
-  <si>
-    <t xml:space="preserve">سعادة مدير الإدارة العامة للمشاريع والصيانة نشير للإيميل الوارد من مدير عام شركة المياه الوطنية بشأن طلب الارتباط على مبلغ 7000 ريال لإيصال خدمة المياه لمركز شرطة القيروان. امل توجيه من ترونه حيال الارتباط على المبلغ المذكور أعلاه وتزويدنا بأصل التعميد ليتنسى لنا على ضوءه افادتهم بذلك .ولسعادتكم تحياتي مدير قسم الاشراف </t>
-  </si>
-  <si>
-    <t>الرد النموذجي أكثر بساطة ووضوحًا في صياغة الطلب.  يُفضل استخدام عبارات أكثر مباشرةً مثل 'نرجو من سعادتكم' بدلاً من 'ونحيط سعادتكم علمًا'.</t>
+    <t xml:space="preserve">سعادة مدير الإدارة العامة للمشاريع والصيانة
+السلام عليكم ورحمة الله وبركاته:
+نشير إلى الإيميل الوارد من مدير عام شركة المياه الوطنية، والذي يتضمّن
+تقديم طلب ارتباط مالي بمبلغ وقدره **٤٬٨٢٠** ريالًا سعوديًا لإيصال خدمة
+المياه لمركز شرطة الملز.
+وعلى أساس ذلك، نأمل من سعادتكم توجيه ما ترونه مناسبًا حول الارتباط
+بالمبلغ المذكور أعلاه، والتفضل بتزويدنا بأصل التعميد؛ ليتسنى لنا إعلام
+الجهات ذات العلاقة وإكمال الإجراءات اللازمة على ضوء ذلك.
+وتقبلو تحياتي
+مدير قسم الإشراف
+</t>
   </si>
 </sst>
 </file>
@@ -1318,8 +1295,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L27"/>
+  <dimension ref="A1:L21"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="10" max="10" width="23.5" customWidth="1"/>
+    <col min="11" max="11" width="28.75" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="15" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
@@ -1420,10 +1401,10 @@
         <v>26</v>
       </c>
       <c r="H3">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="I3">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J3" t="s">
         <v>27</v>
@@ -1432,15 +1413,15 @@
         <v>28</v>
       </c>
       <c r="L3" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C4" t="s">
         <v>14</v>
@@ -1449,25 +1430,25 @@
         <v>15</v>
       </c>
       <c r="E4" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G4" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H4">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I4">
         <v>8</v>
       </c>
       <c r="J4" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K4" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="L4" t="s">
         <v>21</v>
@@ -1475,10 +1456,10 @@
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C5" t="s">
         <v>14</v>
@@ -1487,28 +1468,28 @@
         <v>15</v>
       </c>
       <c r="E5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G5" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H5">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="I5">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="J5" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="K5" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="L5" t="s">
-        <v>43</v>
+        <v>21</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.2">
@@ -1534,27 +1515,27 @@
         <v>48</v>
       </c>
       <c r="H6">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="I6">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="J6" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="K6" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="L6" t="s">
-        <v>43</v>
+        <v>21</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B7" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C7" t="s">
         <v>14</v>
@@ -1563,63 +1544,63 @@
         <v>15</v>
       </c>
       <c r="E7" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="F7" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="G7" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="H7">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="I7">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="J7" t="s">
-        <v>54</v>
+        <v>27</v>
       </c>
       <c r="K7" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L7" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B8" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C8" t="s">
         <v>14</v>
       </c>
       <c r="D8" t="s">
-        <v>15</v>
+        <v>59</v>
       </c>
       <c r="E8" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="F8" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="G8" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="H8">
+        <v>6</v>
+      </c>
+      <c r="I8">
         <v>8</v>
       </c>
-      <c r="I8">
-        <v>6</v>
-      </c>
       <c r="J8" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="K8" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="L8" t="s">
         <v>21</v>
@@ -1627,37 +1608,37 @@
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="B9" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="C9" t="s">
         <v>14</v>
       </c>
       <c r="D9" t="s">
-        <v>15</v>
+        <v>67</v>
       </c>
       <c r="E9" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="F9" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="G9" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="H9">
+        <v>6</v>
+      </c>
+      <c r="I9">
         <v>8</v>
       </c>
-      <c r="I9">
-        <v>6</v>
-      </c>
       <c r="J9" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="K9" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="L9" t="s">
         <v>21</v>
@@ -1665,37 +1646,37 @@
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="B10" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="C10" t="s">
         <v>14</v>
       </c>
       <c r="D10" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="E10" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="F10" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G10" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="H10">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="I10">
         <v>8</v>
       </c>
       <c r="J10" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="K10" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="L10" t="s">
         <v>21</v>
@@ -1703,25 +1684,25 @@
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="B11" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="C11" t="s">
         <v>14</v>
       </c>
       <c r="D11" t="s">
-        <v>15</v>
+        <v>67</v>
       </c>
       <c r="E11" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="F11" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="G11" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="H11">
         <v>6</v>
@@ -1730,10 +1711,10 @@
         <v>8</v>
       </c>
       <c r="J11" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="K11" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="L11" t="s">
         <v>21</v>
@@ -1741,37 +1722,37 @@
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B12" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="C12" t="s">
         <v>14</v>
       </c>
       <c r="D12" t="s">
-        <v>87</v>
+        <v>67</v>
       </c>
       <c r="E12" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F12" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G12" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H12">
         <v>4</v>
       </c>
       <c r="I12">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J12" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="K12" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="L12" t="s">
         <v>21</v>
@@ -1788,7 +1769,7 @@
         <v>14</v>
       </c>
       <c r="D13" t="s">
-        <v>87</v>
+        <v>67</v>
       </c>
       <c r="E13" t="s">
         <v>95</v>
@@ -1803,7 +1784,7 @@
         <v>4</v>
       </c>
       <c r="I13">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J13" t="s">
         <v>98</v>
@@ -1826,7 +1807,7 @@
         <v>14</v>
       </c>
       <c r="D14" t="s">
-        <v>87</v>
+        <v>67</v>
       </c>
       <c r="E14" t="s">
         <v>102</v>
@@ -1838,10 +1819,10 @@
         <v>104</v>
       </c>
       <c r="H14">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J14" t="s">
         <v>105</v>
@@ -1864,7 +1845,7 @@
         <v>14</v>
       </c>
       <c r="D15" t="s">
-        <v>87</v>
+        <v>67</v>
       </c>
       <c r="E15" t="s">
         <v>109</v>
@@ -1876,10 +1857,10 @@
         <v>111</v>
       </c>
       <c r="H15">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I15">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J15" t="s">
         <v>112</v>
@@ -1902,7 +1883,7 @@
         <v>14</v>
       </c>
       <c r="D16" t="s">
-        <v>87</v>
+        <v>67</v>
       </c>
       <c r="E16" t="s">
         <v>116</v>
@@ -1914,54 +1895,54 @@
         <v>118</v>
       </c>
       <c r="H16">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="I16">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="J16" t="s">
-        <v>119</v>
+        <v>27</v>
       </c>
       <c r="K16" t="s">
-        <v>120</v>
+        <v>56</v>
       </c>
       <c r="L16" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="B17" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="C17" t="s">
         <v>14</v>
       </c>
       <c r="D17" t="s">
-        <v>87</v>
+        <v>67</v>
       </c>
       <c r="E17" t="s">
+        <v>121</v>
+      </c>
+      <c r="F17" t="s">
+        <v>122</v>
+      </c>
+      <c r="G17" t="s">
         <v>123</v>
       </c>
-      <c r="F17" t="s">
+      <c r="H17">
+        <v>8</v>
+      </c>
+      <c r="I17">
+        <v>9</v>
+      </c>
+      <c r="J17" t="s">
         <v>124</v>
       </c>
-      <c r="G17" t="s">
+      <c r="K17" t="s">
         <v>125</v>
-      </c>
-      <c r="H17">
-        <v>6</v>
-      </c>
-      <c r="I17">
-        <v>7</v>
-      </c>
-      <c r="J17" t="s">
-        <v>126</v>
-      </c>
-      <c r="K17" t="s">
-        <v>127</v>
       </c>
       <c r="L17" t="s">
         <v>21</v>
@@ -1969,75 +1950,75 @@
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="B18" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="C18" t="s">
         <v>14</v>
       </c>
       <c r="D18" t="s">
-        <v>87</v>
+        <v>59</v>
       </c>
       <c r="E18" t="s">
+        <v>128</v>
+      </c>
+      <c r="F18" t="s">
+        <v>129</v>
+      </c>
+      <c r="G18" t="s">
         <v>130</v>
       </c>
-      <c r="F18" t="s">
-        <v>131</v>
-      </c>
-      <c r="G18" t="s">
-        <v>132</v>
-      </c>
       <c r="H18">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="I18">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="J18" t="s">
-        <v>133</v>
+        <v>27</v>
       </c>
       <c r="K18" t="s">
-        <v>134</v>
+        <v>56</v>
       </c>
       <c r="L18" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="B19" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="C19" t="s">
         <v>14</v>
       </c>
       <c r="D19" t="s">
-        <v>87</v>
+        <v>15</v>
       </c>
       <c r="E19" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="F19" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="G19" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="H19">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="I19">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J19" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="K19" t="s">
-        <v>141</v>
+        <v>20</v>
       </c>
       <c r="L19" t="s">
         <v>21</v>
@@ -2045,278 +2026,50 @@
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="B20" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="C20" t="s">
         <v>14</v>
       </c>
       <c r="D20" t="s">
-        <v>87</v>
+        <v>15</v>
       </c>
       <c r="E20" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="F20" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="G20" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="H20">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="I20">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="J20" t="s">
-        <v>147</v>
+        <v>27</v>
       </c>
       <c r="K20" t="s">
-        <v>148</v>
+        <v>56</v>
       </c>
       <c r="L20" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A21" t="s">
-        <v>149</v>
-      </c>
-      <c r="B21" t="s">
-        <v>150</v>
-      </c>
-      <c r="C21" t="s">
-        <v>14</v>
-      </c>
-      <c r="D21" t="s">
-        <v>72</v>
-      </c>
-      <c r="E21" t="s">
-        <v>151</v>
-      </c>
-      <c r="F21" t="s">
-        <v>152</v>
-      </c>
-      <c r="G21" t="s">
-        <v>153</v>
-      </c>
       <c r="H21">
-        <v>4</v>
+        <f>AVERAGE(H2:H20)</f>
+        <v>6.7894736842105265</v>
       </c>
       <c r="I21">
-        <v>8</v>
-      </c>
-      <c r="J21" t="s">
-        <v>154</v>
-      </c>
-      <c r="K21" t="s">
-        <v>155</v>
-      </c>
-      <c r="L21" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A22" t="s">
-        <v>156</v>
-      </c>
-      <c r="B22" t="s">
-        <v>157</v>
-      </c>
-      <c r="C22" t="s">
-        <v>14</v>
-      </c>
-      <c r="D22" t="s">
-        <v>15</v>
-      </c>
-      <c r="E22" t="s">
-        <v>158</v>
-      </c>
-      <c r="F22" t="s">
-        <v>159</v>
-      </c>
-      <c r="G22" t="s">
-        <v>160</v>
-      </c>
-      <c r="H22">
-        <v>3</v>
-      </c>
-      <c r="I22">
-        <v>6</v>
-      </c>
-      <c r="J22" t="s">
-        <v>161</v>
-      </c>
-      <c r="K22" t="s">
-        <v>162</v>
-      </c>
-      <c r="L22" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A23" t="s">
-        <v>163</v>
-      </c>
-      <c r="B23" t="s">
-        <v>164</v>
-      </c>
-      <c r="C23" t="s">
-        <v>14</v>
-      </c>
-      <c r="D23" t="s">
-        <v>15</v>
-      </c>
-      <c r="E23" t="s">
-        <v>165</v>
-      </c>
-      <c r="F23" t="s">
-        <v>166</v>
-      </c>
-      <c r="G23" t="s">
-        <v>167</v>
-      </c>
-      <c r="H23">
-        <v>7</v>
-      </c>
-      <c r="I23">
-        <v>8</v>
-      </c>
-      <c r="J23" t="s">
-        <v>168</v>
-      </c>
-      <c r="K23" t="s">
-        <v>169</v>
-      </c>
-      <c r="L23" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A24" t="s">
-        <v>170</v>
-      </c>
-      <c r="B24" t="s">
-        <v>171</v>
-      </c>
-      <c r="C24" t="s">
-        <v>14</v>
-      </c>
-      <c r="D24" t="s">
-        <v>15</v>
-      </c>
-      <c r="E24" t="s">
-        <v>172</v>
-      </c>
-      <c r="F24" t="s">
-        <v>173</v>
-      </c>
-      <c r="G24" t="s">
-        <v>174</v>
-      </c>
-      <c r="H24">
-        <v>8</v>
-      </c>
-      <c r="I24">
-        <v>7</v>
-      </c>
-      <c r="J24" t="s">
-        <v>175</v>
-      </c>
-      <c r="K24" t="s">
-        <v>176</v>
-      </c>
-      <c r="L24" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A25" t="s">
-        <v>177</v>
-      </c>
-      <c r="B25" t="s">
-        <v>178</v>
-      </c>
-      <c r="C25" t="s">
-        <v>14</v>
-      </c>
-      <c r="D25" t="s">
-        <v>15</v>
-      </c>
-      <c r="E25" t="s">
-        <v>179</v>
-      </c>
-      <c r="F25" t="s">
-        <v>180</v>
-      </c>
-      <c r="G25" t="s">
-        <v>181</v>
-      </c>
-      <c r="H25">
-        <v>7</v>
-      </c>
-      <c r="I25">
-        <v>6</v>
-      </c>
-      <c r="J25" t="s">
-        <v>182</v>
-      </c>
-      <c r="K25" t="s">
-        <v>183</v>
-      </c>
-      <c r="L25" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A26" t="s">
-        <v>184</v>
-      </c>
-      <c r="B26" t="s">
-        <v>185</v>
-      </c>
-      <c r="C26" t="s">
-        <v>14</v>
-      </c>
-      <c r="D26" t="s">
-        <v>15</v>
-      </c>
-      <c r="E26" t="s">
-        <v>186</v>
-      </c>
-      <c r="F26" t="s">
-        <v>187</v>
-      </c>
-      <c r="G26" t="s">
-        <v>188</v>
-      </c>
-      <c r="H26">
-        <v>7</v>
-      </c>
-      <c r="I26">
-        <v>6</v>
-      </c>
-      <c r="J26" t="s">
-        <v>189</v>
-      </c>
-      <c r="K26" t="s">
-        <v>183</v>
-      </c>
-      <c r="L26" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="H27">
-        <f>AVERAGE(H2:H26)</f>
-        <v>5.44</v>
-      </c>
-      <c r="I27">
-        <f>AVERAGE(I2:I26)</f>
-        <v>7.04</v>
+        <f>AVERAGE(I2:I20)</f>
+        <v>8.473684210526315</v>
       </c>
     </row>
   </sheetData>
